--- a/public/data/systems/pds/public_recent_12m_returns.xlsx
+++ b/public/data/systems/pds/public_recent_12m_returns.xlsx
@@ -79,10 +79,10 @@
         </is>
       </c>
       <c r="B2" s="1">
-        <v>0.03480732327257319</v>
+        <v>0.03480732327257297</v>
       </c>
       <c r="C2" s="1">
-        <v>0.0574380737802096</v>
+        <v>0.05743807378020938</v>
       </c>
       <c r="D2" s="1">
         <v>0.09694350871302371</v>
@@ -103,7 +103,7 @@
         </is>
       </c>
       <c r="B3" s="1">
-        <v>-0.05786896499436156</v>
+        <v>-0.05786896499436178</v>
       </c>
       <c r="C3" s="1">
         <v>-0.05040038243594258</v>
@@ -127,10 +127,10 @@
         </is>
       </c>
       <c r="B4" s="1">
-        <v>-0.006349158442716551</v>
+        <v>-0.006349158442716663</v>
       </c>
       <c r="C4" s="1">
-        <v>-0.02348466316260089</v>
+        <v>-0.023484663162601</v>
       </c>
       <c r="D4" s="1">
         <v>-0.03191397779272764</v>
@@ -151,10 +151,10 @@
         </is>
       </c>
       <c r="B5" s="1">
-        <v>0.07552317289300148</v>
+        <v>0.0755231728930017</v>
       </c>
       <c r="C5" s="1">
-        <v>0.06808226086391156</v>
+        <v>0.06808226086391223</v>
       </c>
       <c r="D5" s="1">
         <v>0.08241348173635221</v>
@@ -175,7 +175,7 @@
         </is>
       </c>
       <c r="B6" s="1">
-        <v>0.08283398244173745</v>
+        <v>0.08283398244173679</v>
       </c>
       <c r="C6" s="1">
         <v>0.09366031117092977</v>
@@ -199,7 +199,7 @@
         </is>
       </c>
       <c r="B7" s="1">
-        <v>-0.05253881478963929</v>
+        <v>-0.05253881478963918</v>
       </c>
       <c r="C7" s="1">
         <v>-0.07517036315416503</v>
@@ -223,10 +223,10 @@
         </is>
       </c>
       <c r="B8" s="1">
-        <v>0.05355638169302601</v>
+        <v>0.05355638169302579</v>
       </c>
       <c r="C8" s="1">
-        <v>0.05250465133473847</v>
+        <v>0.05250465133473825</v>
       </c>
       <c r="D8" s="1">
         <v>0.02882605578313768</v>
@@ -247,13 +247,13 @@
         </is>
       </c>
       <c r="B9" s="1">
-        <v>0.07131809492872576</v>
+        <v>0.07131809492872621</v>
       </c>
       <c r="C9" s="1">
-        <v>0.07501567669311315</v>
+        <v>0.07501567669311382</v>
       </c>
       <c r="D9" s="1">
-        <v>0.06981911041443878</v>
+        <v>0.06981911041443856</v>
       </c>
       <c r="E9" s="1">
         <v>0.07672062522383749</v>
@@ -271,13 +271,13 @@
         </is>
       </c>
       <c r="B10" s="1">
-        <v>0.01172032913814469</v>
+        <v>0.01172033354700242</v>
       </c>
       <c r="C10" s="1">
-        <v>0.02014078802397035</v>
+        <v>0.02014079246952249</v>
       </c>
       <c r="D10" s="1">
-        <v>0.02426734783161422</v>
+        <v>0.02426736573153088</v>
       </c>
       <c r="E10" s="1">
         <v>0.01875739130038356</v>
@@ -295,13 +295,13 @@
         </is>
       </c>
       <c r="B11" s="1">
-        <v>0.01166436694925865</v>
+        <v>0.01166436654146463</v>
       </c>
       <c r="C11" s="1">
-        <v>-0.001187421011046852</v>
+        <v>-0.001187421413659462</v>
       </c>
       <c r="D11" s="1">
-        <v>-0.004492382346648616</v>
+        <v>-0.004492383953884516</v>
       </c>
       <c r="E11" s="1">
         <v>-8.424117964411781e-05</v>
@@ -319,13 +319,13 @@
         </is>
       </c>
       <c r="B12" s="1">
-        <v>0.05056190336976485</v>
+        <v>0.0505619033407918</v>
       </c>
       <c r="C12" s="1">
-        <v>0.04306511815919678</v>
+        <v>0.04306511813043135</v>
       </c>
       <c r="D12" s="1">
-        <v>0.03904010182921303</v>
+        <v>0.03904010173931471</v>
       </c>
       <c r="E12" s="1">
         <v>0.04441029709841615</v>
@@ -343,13 +343,13 @@
         </is>
       </c>
       <c r="B13" s="1">
-        <v>0.0735589997215651</v>
+        <v>0.07355899956890588</v>
       </c>
       <c r="C13" s="1">
-        <v>0.06663034656525979</v>
+        <v>0.06663034641358645</v>
       </c>
       <c r="D13" s="1">
-        <v>0.07878100736579507</v>
+        <v>0.07878100653855347</v>
       </c>
       <c r="E13" s="1">
         <v>0.06259112018290036</v>
@@ -435,7 +435,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0db2b61560d1e414365fe9bf26d5b65bed568421a07cfe32bf0fe1501c3c2270</t>
+          <t>26e6441272432927dd6cf47913d5881beb338d04fa5313bbabef66e34ef6d0f7</t>
         </is>
       </c>
     </row>

--- a/public/data/systems/pds/public_recent_12m_returns.xlsx
+++ b/public/data/systems/pds/public_recent_12m_returns.xlsx
@@ -103,7 +103,7 @@
         </is>
       </c>
       <c r="B3" s="1">
-        <v>-0.05786896499436178</v>
+        <v>-0.05786896499436156</v>
       </c>
       <c r="C3" s="1">
         <v>-0.05040038243594258</v>
@@ -127,7 +127,7 @@
         </is>
       </c>
       <c r="B4" s="1">
-        <v>-0.006349158442716663</v>
+        <v>-0.00634915844271644</v>
       </c>
       <c r="C4" s="1">
         <v>-0.023484663162601</v>
@@ -151,13 +151,13 @@
         </is>
       </c>
       <c r="B5" s="1">
-        <v>0.0755231728930017</v>
+        <v>0.07552316951068638</v>
       </c>
       <c r="C5" s="1">
-        <v>0.06808226086391223</v>
+        <v>0.06808225750499752</v>
       </c>
       <c r="D5" s="1">
-        <v>0.08241348173635221</v>
+        <v>0.08241346862975285</v>
       </c>
       <c r="E5" s="1">
         <v>0.06328154521851803</v>
@@ -175,13 +175,13 @@
         </is>
       </c>
       <c r="B6" s="1">
-        <v>0.08283398244173679</v>
+        <v>0.08283398504563766</v>
       </c>
       <c r="C6" s="1">
-        <v>0.09366031117092977</v>
+        <v>0.09366031380086359</v>
       </c>
       <c r="D6" s="1">
-        <v>0.1379985504593355</v>
+        <v>0.1379985611022643</v>
       </c>
       <c r="E6" s="1">
         <v>0.07894705376009514</v>
@@ -199,13 +199,13 @@
         </is>
       </c>
       <c r="B7" s="1">
-        <v>-0.05253881478963918</v>
+        <v>-0.05253880981801506</v>
       </c>
       <c r="C7" s="1">
-        <v>-0.07517036315416503</v>
+        <v>-0.07517035830129581</v>
       </c>
       <c r="D7" s="1">
-        <v>-0.08649242841708982</v>
+        <v>-0.0864924086562967</v>
       </c>
       <c r="E7" s="1">
         <v>-0.07137570738535337</v>
@@ -223,13 +223,13 @@
         </is>
       </c>
       <c r="B8" s="1">
-        <v>0.05355638169302579</v>
+        <v>0.05355637512961198</v>
       </c>
       <c r="C8" s="1">
-        <v>0.05250465133473825</v>
+        <v>0.05250464477787586</v>
       </c>
       <c r="D8" s="1">
-        <v>0.02882605578313768</v>
+        <v>0.02882602930971068</v>
       </c>
       <c r="E8" s="1">
         <v>0.06040571692215058</v>
@@ -247,13 +247,13 @@
         </is>
       </c>
       <c r="B9" s="1">
-        <v>0.07131809492872621</v>
+        <v>0.07131809554506763</v>
       </c>
       <c r="C9" s="1">
-        <v>0.07501567669311382</v>
+        <v>0.07501567731158287</v>
       </c>
       <c r="D9" s="1">
-        <v>0.06981911041443856</v>
+        <v>0.0698191124061458</v>
       </c>
       <c r="E9" s="1">
         <v>0.07672062522383749</v>
@@ -271,13 +271,13 @@
         </is>
       </c>
       <c r="B10" s="1">
-        <v>0.01172033354700242</v>
+        <v>0.01172033827795826</v>
       </c>
       <c r="C10" s="1">
-        <v>0.02014079246952249</v>
+        <v>0.02014079723985462</v>
       </c>
       <c r="D10" s="1">
-        <v>0.02426736573153088</v>
+        <v>0.02426738493593339</v>
       </c>
       <c r="E10" s="1">
         <v>0.01875739130038356</v>
@@ -295,13 +295,13 @@
         </is>
       </c>
       <c r="B11" s="1">
-        <v>0.01166436654146463</v>
+        <v>0.01166434752247358</v>
       </c>
       <c r="C11" s="1">
-        <v>-0.001187421413659462</v>
+        <v>-0.001187440191040889</v>
       </c>
       <c r="D11" s="1">
-        <v>-0.004492383953884516</v>
+        <v>-0.004492459142703464</v>
       </c>
       <c r="E11" s="1">
         <v>-8.424117964411781e-05</v>
@@ -319,13 +319,13 @@
         </is>
       </c>
       <c r="B12" s="1">
-        <v>0.0505619033407918</v>
+        <v>0.05056190959753537</v>
       </c>
       <c r="C12" s="1">
-        <v>0.04306511813043135</v>
+        <v>0.04306512434252574</v>
       </c>
       <c r="D12" s="1">
-        <v>0.03904010173931471</v>
+        <v>0.03904012690016345</v>
       </c>
       <c r="E12" s="1">
         <v>0.04441029709841615</v>
@@ -343,13 +343,13 @@
         </is>
       </c>
       <c r="B13" s="1">
-        <v>0.07355899956890588</v>
+        <v>0.07355900649362779</v>
       </c>
       <c r="C13" s="1">
-        <v>0.06663034641358645</v>
+        <v>0.06663035329361588</v>
       </c>
       <c r="D13" s="1">
-        <v>0.07878100653855347</v>
+        <v>0.07878103466853603</v>
       </c>
       <c r="E13" s="1">
         <v>0.06259112018290036</v>
@@ -435,7 +435,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>26e6441272432927dd6cf47913d5881beb338d04fa5313bbabef66e34ef6d0f7</t>
+          <t>cac41a59a75d12273ed1c4e403396036bbbab18b41cadcd3ef4cf8561cca0489</t>
         </is>
       </c>
     </row>

--- a/public/data/systems/pds/public_recent_12m_returns.xlsx
+++ b/public/data/systems/pds/public_recent_12m_returns.xlsx
@@ -127,10 +127,10 @@
         </is>
       </c>
       <c r="B4" s="1">
-        <v>-0.00634915844271644</v>
+        <v>-0.006349158442716996</v>
       </c>
       <c r="C4" s="1">
-        <v>-0.023484663162601</v>
+        <v>-0.02348466316260078</v>
       </c>
       <c r="D4" s="1">
         <v>-0.03191397779272764</v>
@@ -151,10 +151,10 @@
         </is>
       </c>
       <c r="B5" s="1">
-        <v>0.07552316951068638</v>
+        <v>0.07552316951068616</v>
       </c>
       <c r="C5" s="1">
-        <v>0.06808225750499752</v>
+        <v>0.0680822575049973</v>
       </c>
       <c r="D5" s="1">
         <v>0.08241346862975285</v>
@@ -175,13 +175,13 @@
         </is>
       </c>
       <c r="B6" s="1">
-        <v>0.08283398504563766</v>
+        <v>0.08283398503169637</v>
       </c>
       <c r="C6" s="1">
-        <v>0.09366031380086359</v>
+        <v>0.09366031378678441</v>
       </c>
       <c r="D6" s="1">
-        <v>0.1379985611022643</v>
+        <v>0.1379985609456906</v>
       </c>
       <c r="E6" s="1">
         <v>0.07894705376009514</v>
@@ -199,13 +199,13 @@
         </is>
       </c>
       <c r="B7" s="1">
-        <v>-0.05253880981801506</v>
+        <v>-0.05253880932984711</v>
       </c>
       <c r="C7" s="1">
-        <v>-0.07517035830129581</v>
+        <v>-0.07517035782478798</v>
       </c>
       <c r="D7" s="1">
-        <v>-0.0864924086562967</v>
+        <v>-0.08649240688109705</v>
       </c>
       <c r="E7" s="1">
         <v>-0.07137570738535337</v>
@@ -223,13 +223,13 @@
         </is>
       </c>
       <c r="B8" s="1">
-        <v>0.05355637512961198</v>
+        <v>0.05355636931291152</v>
       </c>
       <c r="C8" s="1">
-        <v>0.05250464477787586</v>
+        <v>0.05250463896698299</v>
       </c>
       <c r="D8" s="1">
-        <v>0.02882602930971068</v>
+        <v>0.02882600668426938</v>
       </c>
       <c r="E8" s="1">
         <v>0.06040571692215058</v>
@@ -247,13 +247,13 @@
         </is>
       </c>
       <c r="B9" s="1">
-        <v>0.07131809554506763</v>
+        <v>0.07131810113707027</v>
       </c>
       <c r="C9" s="1">
-        <v>0.07501567731158287</v>
+        <v>0.07501568292288519</v>
       </c>
       <c r="D9" s="1">
-        <v>0.0698191124061458</v>
+        <v>0.0698191348886763</v>
       </c>
       <c r="E9" s="1">
         <v>0.07672062522383749</v>
@@ -271,13 +271,13 @@
         </is>
       </c>
       <c r="B10" s="1">
-        <v>0.01172033827795826</v>
+        <v>0.01172032754400765</v>
       </c>
       <c r="C10" s="1">
-        <v>0.02014079723985462</v>
+        <v>0.02014078641656591</v>
       </c>
       <c r="D10" s="1">
-        <v>0.02426738493593339</v>
+        <v>0.02426734115994122</v>
       </c>
       <c r="E10" s="1">
         <v>0.01875739130038356</v>
@@ -295,13 +295,13 @@
         </is>
       </c>
       <c r="B11" s="1">
-        <v>0.01166434752247358</v>
+        <v>0.01166436420034844</v>
       </c>
       <c r="C11" s="1">
-        <v>-0.001187440191040889</v>
+        <v>-0.001187423725035885</v>
       </c>
       <c r="D11" s="1">
-        <v>-0.004492459142703464</v>
+        <v>-0.004492393244840631</v>
       </c>
       <c r="E11" s="1">
         <v>-8.424117964411781e-05</v>
@@ -319,13 +319,13 @@
         </is>
       </c>
       <c r="B12" s="1">
-        <v>0.05056190959753537</v>
+        <v>0.05056190323773468</v>
       </c>
       <c r="C12" s="1">
-        <v>0.04306512434252574</v>
+        <v>0.04306511802810875</v>
       </c>
       <c r="D12" s="1">
-        <v>0.03904012690016345</v>
+        <v>0.03904010192097451</v>
       </c>
       <c r="E12" s="1">
         <v>0.04441029709841615</v>
@@ -343,13 +343,13 @@
         </is>
       </c>
       <c r="B13" s="1">
-        <v>0.07355900649362779</v>
+        <v>0.07355900644611224</v>
       </c>
       <c r="C13" s="1">
-        <v>0.06663035329361588</v>
+        <v>0.06663035324640831</v>
       </c>
       <c r="D13" s="1">
-        <v>0.07878103466853603</v>
+        <v>0.07878103445972551</v>
       </c>
       <c r="E13" s="1">
         <v>0.06259112018290036</v>
@@ -435,7 +435,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>cac41a59a75d12273ed1c4e403396036bbbab18b41cadcd3ef4cf8561cca0489</t>
+          <t>18981769cd14cfc61429588a8a3410beafce390a9aeacec1214f0c5b7fc9efaf</t>
         </is>
       </c>
     </row>

--- a/public/data/systems/pds/public_recent_12m_returns.xlsx
+++ b/public/data/systems/pds/public_recent_12m_returns.xlsx
@@ -79,16 +79,16 @@
         </is>
       </c>
       <c r="B2" s="1">
-        <v>0.03480732327257297</v>
+        <v>0.03480731534083659</v>
       </c>
       <c r="C2" s="1">
-        <v>0.05743807378020938</v>
+        <v>0.05743806567500931</v>
       </c>
       <c r="D2" s="1">
-        <v>0.09694350871302371</v>
+        <v>0.09694350417347875</v>
       </c>
       <c r="E2" s="1">
-        <v>0.04437254080456055</v>
+        <v>0.0443725315029373</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -103,16 +103,16 @@
         </is>
       </c>
       <c r="B3" s="1">
-        <v>-0.05786896499436156</v>
+        <v>-0.05786895063313491</v>
       </c>
       <c r="C3" s="1">
-        <v>-0.05040038243594258</v>
+        <v>-0.05040036796086989</v>
       </c>
       <c r="D3" s="1">
-        <v>-0.07173192787694704</v>
+        <v>-0.07173191703910431</v>
       </c>
       <c r="E3" s="1">
-        <v>-0.04327052859411606</v>
+        <v>-0.0432705128927402</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -127,16 +127,16 @@
         </is>
       </c>
       <c r="B4" s="1">
-        <v>-0.006349158442716996</v>
+        <v>-0.00634916502585936</v>
       </c>
       <c r="C4" s="1">
-        <v>-0.02348466316260078</v>
+        <v>-0.02348466963221751</v>
       </c>
       <c r="D4" s="1">
-        <v>-0.03191397779272764</v>
+        <v>-0.03191398933217382</v>
       </c>
       <c r="E4" s="1">
-        <v>-0.02069780714412506</v>
+        <v>-0.02069781193868203</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -151,16 +151,16 @@
         </is>
       </c>
       <c r="B5" s="1">
-        <v>0.07552316951068616</v>
+        <v>0.07552314898626977</v>
       </c>
       <c r="C5" s="1">
-        <v>0.0680822575049973</v>
+        <v>0.06808223712257688</v>
       </c>
       <c r="D5" s="1">
         <v>0.08241346862975285</v>
       </c>
       <c r="E5" s="1">
-        <v>0.06328154521851803</v>
+        <v>0.06328151779554969</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -175,16 +175,16 @@
         </is>
       </c>
       <c r="B6" s="1">
-        <v>0.08283398503169637</v>
+        <v>0.08283401362029075</v>
       </c>
       <c r="C6" s="1">
-        <v>0.09366031378678441</v>
+        <v>0.09366034266121059</v>
       </c>
       <c r="D6" s="1">
-        <v>0.1379985609456906</v>
+        <v>0.1379985708516547</v>
       </c>
       <c r="E6" s="1">
-        <v>0.07894705376009514</v>
+        <v>0.07894708896267</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -199,16 +199,16 @@
         </is>
       </c>
       <c r="B7" s="1">
-        <v>-0.05253880932984711</v>
+        <v>-0.05253881997978804</v>
       </c>
       <c r="C7" s="1">
-        <v>-0.07517035782478798</v>
+        <v>-0.07517036822033918</v>
       </c>
       <c r="D7" s="1">
-        <v>-0.08649240688109705</v>
+        <v>-0.08649244024499136</v>
       </c>
       <c r="E7" s="1">
-        <v>-0.07137570738535337</v>
+        <v>-0.07137571016066713</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -223,16 +223,16 @@
         </is>
       </c>
       <c r="B8" s="1">
-        <v>0.05355636931291152</v>
+        <v>0.05355636918410434</v>
       </c>
       <c r="C8" s="1">
-        <v>0.05250463896698299</v>
+        <v>0.05250463883830458</v>
       </c>
       <c r="D8" s="1">
-        <v>0.02882600668426938</v>
+        <v>0.02882606952228151</v>
       </c>
       <c r="E8" s="1">
-        <v>0.06040571692215058</v>
+        <v>0.06040569538379836</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -247,16 +247,16 @@
         </is>
       </c>
       <c r="B9" s="1">
-        <v>0.07131810113707027</v>
+        <v>0.07131811504061591</v>
       </c>
       <c r="C9" s="1">
-        <v>0.07501568292288519</v>
+        <v>0.07501569687441934</v>
       </c>
       <c r="D9" s="1">
-        <v>0.0698191348886763</v>
+        <v>0.06981910404711988</v>
       </c>
       <c r="E9" s="1">
-        <v>0.07672062522383749</v>
+        <v>0.07672065442117004</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -271,16 +271,16 @@
         </is>
       </c>
       <c r="B10" s="1">
-        <v>0.01172032754400765</v>
+        <v>0.01172031964157094</v>
       </c>
       <c r="C10" s="1">
-        <v>0.02014078641656591</v>
+        <v>0.02014077844835782</v>
       </c>
       <c r="D10" s="1">
-        <v>0.02426734115994122</v>
+        <v>0.02426732457418801</v>
       </c>
       <c r="E10" s="1">
-        <v>0.01875739130038356</v>
+        <v>0.01875738625260026</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -295,16 +295,16 @@
         </is>
       </c>
       <c r="B11" s="1">
-        <v>0.01166436420034844</v>
+        <v>0.01166437916766294</v>
       </c>
       <c r="C11" s="1">
-        <v>-0.001187423725035885</v>
+        <v>-0.00118740894786018</v>
       </c>
       <c r="D11" s="1">
-        <v>-0.004492393244840631</v>
+        <v>-0.004492362893525503</v>
       </c>
       <c r="E11" s="1">
-        <v>-8.424117964411781e-05</v>
+        <v>-8.423166016624517e-05</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -319,16 +319,16 @@
         </is>
       </c>
       <c r="B12" s="1">
-        <v>0.05056190323773468</v>
+        <v>0.05056189595293414</v>
       </c>
       <c r="C12" s="1">
-        <v>0.04306511802810875</v>
+        <v>0.04306511079529218</v>
       </c>
       <c r="D12" s="1">
-        <v>0.03904010192097451</v>
+        <v>0.03904010559224491</v>
       </c>
       <c r="E12" s="1">
-        <v>0.04441029709841615</v>
+        <v>0.04441028605487785</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -343,16 +343,16 @@
         </is>
       </c>
       <c r="B13" s="1">
-        <v>0.07355900644611224</v>
+        <v>0.07355900764141787</v>
       </c>
       <c r="C13" s="1">
-        <v>0.06663035324640831</v>
+        <v>0.06663035443399901</v>
       </c>
       <c r="D13" s="1">
-        <v>0.07878103445972551</v>
+        <v>0.0787810137804299</v>
       </c>
       <c r="E13" s="1">
-        <v>0.06259112018290036</v>
+        <v>0.06259112856481486</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -435,7 +435,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>18981769cd14cfc61429588a8a3410beafce390a9aeacec1214f0c5b7fc9efaf</t>
+          <t>44e9bddf3279d82fd1f1c87bc5b11efae68a4af16ad556b3b7f74a9b19eeb0b6</t>
         </is>
       </c>
     </row>

--- a/public/data/systems/pds/public_recent_12m_returns.xlsx
+++ b/public/data/systems/pds/public_recent_12m_returns.xlsx
@@ -79,16 +79,16 @@
         </is>
       </c>
       <c r="B2" s="1">
-        <v>0.03480731534083659</v>
+        <v>0.02712989058195192</v>
       </c>
       <c r="C2" s="1">
-        <v>0.05743806567500931</v>
+        <v>0.04959273923979146</v>
       </c>
       <c r="D2" s="1">
-        <v>0.09694350417347875</v>
+        <v>0.09694349643809308</v>
       </c>
       <c r="E2" s="1">
-        <v>0.0443725315029373</v>
+        <v>0.0443725332928202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -103,16 +103,16 @@
         </is>
       </c>
       <c r="B3" s="1">
-        <v>-0.05786895063313491</v>
+        <v>-0.0536258356002608</v>
       </c>
       <c r="C3" s="1">
-        <v>-0.05040036796086989</v>
+        <v>-0.04612361635967233</v>
       </c>
       <c r="D3" s="1">
-        <v>-0.07173191703910431</v>
+        <v>-0.07173190949844122</v>
       </c>
       <c r="E3" s="1">
-        <v>-0.0432705128927402</v>
+        <v>-0.04327051867383436</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -127,16 +127,16 @@
         </is>
       </c>
       <c r="B4" s="1">
-        <v>-0.00634916502585936</v>
+        <v>-0.004646294272754314</v>
       </c>
       <c r="C4" s="1">
-        <v>-0.02348466963221751</v>
+        <v>-0.0218111648783208</v>
       </c>
       <c r="D4" s="1">
-        <v>-0.03191398933217382</v>
+        <v>-0.03191398347322494</v>
       </c>
       <c r="E4" s="1">
-        <v>-0.02069781193868203</v>
+        <v>-0.02069780503460839</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -151,16 +151,16 @@
         </is>
       </c>
       <c r="B5" s="1">
-        <v>0.07552314898626977</v>
+        <v>0.07262418868335163</v>
       </c>
       <c r="C5" s="1">
-        <v>0.06808223712257688</v>
+        <v>0.06520333302033676</v>
       </c>
       <c r="D5" s="1">
-        <v>0.08241346862975285</v>
+        <v>0.08241344964800246</v>
       </c>
       <c r="E5" s="1">
-        <v>0.06328151779554969</v>
+        <v>0.06328154508771822</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -175,16 +175,16 @@
         </is>
       </c>
       <c r="B6" s="1">
-        <v>0.08283401362029075</v>
+        <v>0.07408960972339385</v>
       </c>
       <c r="C6" s="1">
-        <v>0.09366034266121059</v>
+        <v>0.08482851096590371</v>
       </c>
       <c r="D6" s="1">
-        <v>0.1379985708516547</v>
+        <v>0.1379985923109532</v>
       </c>
       <c r="E6" s="1">
-        <v>0.07894708896267</v>
+        <v>0.07894707670957501</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -199,16 +199,16 @@
         </is>
       </c>
       <c r="B7" s="1">
-        <v>-0.05253881997978804</v>
+        <v>-0.05020755892733453</v>
       </c>
       <c r="C7" s="1">
-        <v>-0.07517036822033918</v>
+        <v>-0.07289479287626333</v>
       </c>
       <c r="D7" s="1">
-        <v>-0.08649244024499136</v>
+        <v>-0.08649243597372347</v>
       </c>
       <c r="E7" s="1">
-        <v>-0.07137571016066713</v>
+        <v>-0.07137571218933358</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -223,16 +223,16 @@
         </is>
       </c>
       <c r="B8" s="1">
-        <v>0.05355636918410434</v>
+        <v>0.05830124929372738</v>
       </c>
       <c r="C8" s="1">
-        <v>0.05250463883830458</v>
+        <v>0.05724478229164109</v>
       </c>
       <c r="D8" s="1">
-        <v>0.02882606952228151</v>
+        <v>0.02882604458055615</v>
       </c>
       <c r="E8" s="1">
-        <v>0.06040569538379836</v>
+        <v>0.06040570583322036</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -247,16 +247,16 @@
         </is>
       </c>
       <c r="B9" s="1">
-        <v>0.07131811504061591</v>
+        <v>0.07233920733030175</v>
       </c>
       <c r="C9" s="1">
-        <v>0.07501569687441934</v>
+        <v>0.07604031339490769</v>
       </c>
       <c r="D9" s="1">
-        <v>0.06981910404711988</v>
+        <v>0.06981911786092621</v>
       </c>
       <c r="E9" s="1">
-        <v>0.07672065442117004</v>
+        <v>0.07672065237946679</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -271,16 +271,16 @@
         </is>
       </c>
       <c r="B10" s="1">
-        <v>0.01172031964157094</v>
+        <v>0.01089758674868802</v>
       </c>
       <c r="C10" s="1">
-        <v>0.02014077844835782</v>
+        <v>0.01931119802231862</v>
       </c>
       <c r="D10" s="1">
-        <v>0.02426732457418801</v>
+        <v>0.02426736217350212</v>
       </c>
       <c r="E10" s="1">
-        <v>0.01875738625260026</v>
+        <v>0.01875736166871977</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -295,16 +295,16 @@
         </is>
       </c>
       <c r="B11" s="1">
-        <v>0.01166437916766294</v>
+        <v>0.01233470487201571</v>
       </c>
       <c r="C11" s="1">
-        <v>-0.00118740894786018</v>
+        <v>-0.0005255987987629052</v>
       </c>
       <c r="D11" s="1">
-        <v>-0.004492362893525503</v>
+        <v>-0.004492408452007934</v>
       </c>
       <c r="E11" s="1">
-        <v>-8.423166016624517e-05</v>
+        <v>-8.423183810102319e-05</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -319,16 +319,16 @@
         </is>
       </c>
       <c r="B12" s="1">
-        <v>0.05056189595293414</v>
+        <v>0.05137457943233836</v>
       </c>
       <c r="C12" s="1">
-        <v>0.04306511079529218</v>
+        <v>0.04387199498436534</v>
       </c>
       <c r="D12" s="1">
-        <v>0.03904010559224491</v>
+        <v>0.03904012411124302</v>
       </c>
       <c r="E12" s="1">
-        <v>0.04441028605487785</v>
+        <v>0.04441027720671853</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -343,16 +343,16 @@
         </is>
       </c>
       <c r="B13" s="1">
-        <v>0.07355900764141787</v>
+        <v>0.07111907728435463</v>
       </c>
       <c r="C13" s="1">
-        <v>0.06663035443399901</v>
+        <v>0.06420617116784832</v>
       </c>
       <c r="D13" s="1">
-        <v>0.0787810137804299</v>
+        <v>0.07878102554379174</v>
       </c>
       <c r="E13" s="1">
-        <v>0.06259112856481486</v>
+        <v>0.06259113938944316</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -435,7 +435,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>44e9bddf3279d82fd1f1c87bc5b11efae68a4af16ad556b3b7f74a9b19eeb0b6</t>
+          <t>8259f1d757204e0b8746505e2c2b509ff445d2cc89ed073ca872dc08d113d845</t>
         </is>
       </c>
     </row>

--- a/public/data/systems/pds/public_recent_12m_returns.xlsx
+++ b/public/data/systems/pds/public_recent_12m_returns.xlsx
@@ -82,7 +82,7 @@
         <v>0.02712989058195192</v>
       </c>
       <c r="C2" s="1">
-        <v>0.04959273923979146</v>
+        <v>0.04959273923979124</v>
       </c>
       <c r="D2" s="1">
         <v>0.09694349643809308</v>
@@ -103,16 +103,16 @@
         </is>
       </c>
       <c r="B3" s="1">
-        <v>-0.0536258356002608</v>
+        <v>-0.05362583829351886</v>
       </c>
       <c r="C3" s="1">
-        <v>-0.04612361635967233</v>
+        <v>-0.04612361907428075</v>
       </c>
       <c r="D3" s="1">
-        <v>-0.07173190949844122</v>
+        <v>-0.07173190963320608</v>
       </c>
       <c r="E3" s="1">
-        <v>-0.04327051867383436</v>
+        <v>-0.04327052168104717</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -127,16 +127,16 @@
         </is>
       </c>
       <c r="B4" s="1">
-        <v>-0.004646294272754314</v>
+        <v>-0.004646289807469506</v>
       </c>
       <c r="C4" s="1">
-        <v>-0.0218111648783208</v>
+        <v>-0.02181116049004017</v>
       </c>
       <c r="D4" s="1">
-        <v>-0.03191398347322494</v>
+        <v>-0.03191398450198579</v>
       </c>
       <c r="E4" s="1">
-        <v>-0.02069780503460839</v>
+        <v>-0.02069780007223643</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -151,16 +151,16 @@
         </is>
       </c>
       <c r="B5" s="1">
-        <v>0.07262418868335163</v>
+        <v>0.07262416620008483</v>
       </c>
       <c r="C5" s="1">
-        <v>0.06520333302033676</v>
+        <v>0.0652033106926182</v>
       </c>
       <c r="D5" s="1">
-        <v>0.08241344964800246</v>
+        <v>0.0824134747624814</v>
       </c>
       <c r="E5" s="1">
-        <v>0.06328154508771822</v>
+        <v>0.06328151741260268</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -175,16 +175,16 @@
         </is>
       </c>
       <c r="B6" s="1">
-        <v>0.07408960972339385</v>
+        <v>0.074089632512361</v>
       </c>
       <c r="C6" s="1">
-        <v>0.08482851096590371</v>
+        <v>0.08482853398271795</v>
       </c>
       <c r="D6" s="1">
-        <v>0.1379985923109532</v>
+        <v>0.1379985660180871</v>
       </c>
       <c r="E6" s="1">
-        <v>0.07894707670957501</v>
+        <v>0.07894710512543757</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -199,16 +199,16 @@
         </is>
       </c>
       <c r="B7" s="1">
-        <v>-0.05020755892733453</v>
+        <v>-0.05020757091970041</v>
       </c>
       <c r="C7" s="1">
-        <v>-0.07289479287626333</v>
+        <v>-0.07289480458217312</v>
       </c>
       <c r="D7" s="1">
-        <v>-0.08649243597372347</v>
+        <v>-0.08649244012688595</v>
       </c>
       <c r="E7" s="1">
-        <v>-0.07137571218933358</v>
+        <v>-0.07137572468494624</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -223,16 +223,16 @@
         </is>
       </c>
       <c r="B8" s="1">
-        <v>0.05830124929372738</v>
+        <v>0.0583012731950483</v>
       </c>
       <c r="C8" s="1">
-        <v>0.05724478229164109</v>
+        <v>0.05724480616910244</v>
       </c>
       <c r="D8" s="1">
-        <v>0.02882604458055615</v>
+        <v>0.02882606803478294</v>
       </c>
       <c r="E8" s="1">
-        <v>0.06040570583322036</v>
+        <v>0.06040572965815794</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -247,16 +247,16 @@
         </is>
       </c>
       <c r="B9" s="1">
-        <v>0.07233920733030175</v>
+        <v>0.07233919770176533</v>
       </c>
       <c r="C9" s="1">
-        <v>0.07604031339490769</v>
+        <v>0.07604030373313897</v>
       </c>
       <c r="D9" s="1">
-        <v>0.06981911786092621</v>
+        <v>0.06981909421788512</v>
       </c>
       <c r="E9" s="1">
-        <v>0.07672065237946679</v>
+        <v>0.07672064417665725</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -271,16 +271,16 @@
         </is>
       </c>
       <c r="B10" s="1">
-        <v>0.01089758674868802</v>
+        <v>0.01089760669413953</v>
       </c>
       <c r="C10" s="1">
-        <v>0.01931119802231862</v>
+        <v>0.01931121813377423</v>
       </c>
       <c r="D10" s="1">
-        <v>0.02426736217350212</v>
+        <v>0.02426737852962968</v>
       </c>
       <c r="E10" s="1">
-        <v>0.01875736166871977</v>
+        <v>0.01875738220060508</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -295,16 +295,16 @@
         </is>
       </c>
       <c r="B11" s="1">
-        <v>0.01233470487201571</v>
+        <v>0.01233471196963953</v>
       </c>
       <c r="C11" s="1">
-        <v>-0.0005255987987629052</v>
+        <v>-0.0005255917913045138</v>
       </c>
       <c r="D11" s="1">
-        <v>-0.004492408452007934</v>
+        <v>-0.004492423755518282</v>
       </c>
       <c r="E11" s="1">
-        <v>-8.423183810102319e-05</v>
+        <v>-8.4222378336829e-05</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -319,16 +319,16 @@
         </is>
       </c>
       <c r="B12" s="1">
-        <v>0.05137457943233836</v>
+        <v>0.05137457237664433</v>
       </c>
       <c r="C12" s="1">
-        <v>0.04387199498436534</v>
+        <v>0.04387198797901926</v>
       </c>
       <c r="D12" s="1">
-        <v>0.03904012411124302</v>
+        <v>0.03904012344334129</v>
       </c>
       <c r="E12" s="1">
-        <v>0.04441027720671853</v>
+        <v>0.04441026948312721</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -343,16 +343,16 @@
         </is>
       </c>
       <c r="B13" s="1">
-        <v>0.07111907728435463</v>
+        <v>0.0711190385970919</v>
       </c>
       <c r="C13" s="1">
-        <v>0.06420617116784832</v>
+        <v>0.06420613273027009</v>
       </c>
       <c r="D13" s="1">
-        <v>0.07878102554379174</v>
+        <v>0.07878099979019582</v>
       </c>
       <c r="E13" s="1">
-        <v>0.06259113938944316</v>
+        <v>0.06259109955039022</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -435,7 +435,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>8259f1d757204e0b8746505e2c2b509ff445d2cc89ed073ca872dc08d113d845</t>
+          <t>2313e90ebeaab0efd698b861dfa32462509b8eda4e8a4d82f6c81e003f867453</t>
         </is>
       </c>
     </row>

--- a/public/data/systems/pds/public_recent_12m_returns.xlsx
+++ b/public/data/systems/pds/public_recent_12m_returns.xlsx
@@ -79,16 +79,16 @@
         </is>
       </c>
       <c r="B2" s="1">
-        <v>0.02712989058195192</v>
+        <v>0.02712989058195125</v>
       </c>
       <c r="C2" s="1">
-        <v>0.04959273923979124</v>
+        <v>0.0495927392397908</v>
       </c>
       <c r="D2" s="1">
         <v>0.09694349643809308</v>
       </c>
       <c r="E2" s="1">
-        <v>0.0443725332928202</v>
+        <v>0.04437253329281998</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -103,16 +103,16 @@
         </is>
       </c>
       <c r="B3" s="1">
-        <v>-0.05362583829351886</v>
+        <v>-0.05362583562908274</v>
       </c>
       <c r="C3" s="1">
-        <v>-0.04612361907428075</v>
+        <v>-0.04612361638872287</v>
       </c>
       <c r="D3" s="1">
-        <v>-0.07173190963320608</v>
+        <v>-0.07173190949844122</v>
       </c>
       <c r="E3" s="1">
-        <v>-0.04327052168104717</v>
+        <v>-0.04327051870610032</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -127,16 +127,16 @@
         </is>
       </c>
       <c r="B4" s="1">
-        <v>-0.004646289807469506</v>
+        <v>-0.004646285493852487</v>
       </c>
       <c r="C4" s="1">
-        <v>-0.02181116049004017</v>
+        <v>-0.02181115625081043</v>
       </c>
       <c r="D4" s="1">
-        <v>-0.03191398450198579</v>
+        <v>-0.03191398347322494</v>
       </c>
       <c r="E4" s="1">
-        <v>-0.02069780007223643</v>
+        <v>-0.02069779542340811</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -151,16 +151,16 @@
         </is>
       </c>
       <c r="B5" s="1">
-        <v>0.07262416620008483</v>
+        <v>0.07262416433683305</v>
       </c>
       <c r="C5" s="1">
-        <v>0.0652033106926182</v>
+        <v>0.06520330884225745</v>
       </c>
       <c r="D5" s="1">
-        <v>0.0824134747624814</v>
+        <v>0.0824134496686979</v>
       </c>
       <c r="E5" s="1">
-        <v>0.06328151741260268</v>
+        <v>0.06328151815016958</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -175,16 +175,16 @@
         </is>
       </c>
       <c r="B6" s="1">
-        <v>0.074089632512361</v>
+        <v>0.07408961995335295</v>
       </c>
       <c r="C6" s="1">
-        <v>0.08482853398271795</v>
+        <v>0.08482852129814389</v>
       </c>
       <c r="D6" s="1">
-        <v>0.1379985660180871</v>
+        <v>0.1379985751862309</v>
       </c>
       <c r="E6" s="1">
-        <v>0.07894710512543757</v>
+        <v>0.07894709005298495</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -199,16 +199,16 @@
         </is>
       </c>
       <c r="B7" s="1">
-        <v>-0.05020757091970041</v>
+        <v>-0.05020756333672527</v>
       </c>
       <c r="C7" s="1">
-        <v>-0.07289480458217312</v>
+        <v>-0.07289479718032899</v>
       </c>
       <c r="D7" s="1">
-        <v>-0.08649244012688595</v>
+        <v>-0.08649242053283257</v>
       </c>
       <c r="E7" s="1">
-        <v>-0.07137572468494624</v>
+        <v>-0.07137571863596992</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -223,16 +223,16 @@
         </is>
       </c>
       <c r="B8" s="1">
-        <v>0.0583012731950483</v>
+        <v>0.058301239724311</v>
       </c>
       <c r="C8" s="1">
-        <v>0.05724480616910244</v>
+        <v>0.05724477273177775</v>
       </c>
       <c r="D8" s="1">
-        <v>0.02882606803478294</v>
+        <v>0.02882604470432648</v>
       </c>
       <c r="E8" s="1">
-        <v>0.06040572965815794</v>
+        <v>0.06040569511254956</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -247,16 +247,16 @@
         </is>
       </c>
       <c r="B9" s="1">
-        <v>0.07233919770176533</v>
+        <v>0.07233921421960976</v>
       </c>
       <c r="C9" s="1">
-        <v>0.07604030373313897</v>
+        <v>0.07604032030799313</v>
       </c>
       <c r="D9" s="1">
-        <v>0.06981909421788512</v>
+        <v>0.06981909532256569</v>
       </c>
       <c r="E9" s="1">
-        <v>0.07672064417665725</v>
+        <v>0.07672066252334653</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -271,16 +271,16 @@
         </is>
       </c>
       <c r="B10" s="1">
-        <v>0.01089760669413953</v>
+        <v>0.01089759907241317</v>
       </c>
       <c r="C10" s="1">
-        <v>0.01931121813377423</v>
+        <v>0.01931121044861328</v>
       </c>
       <c r="D10" s="1">
-        <v>0.02426737852962968</v>
+        <v>0.02426733085800836</v>
       </c>
       <c r="E10" s="1">
-        <v>0.01875738220060508</v>
+        <v>0.01875737896088747</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -295,16 +295,16 @@
         </is>
       </c>
       <c r="B11" s="1">
-        <v>0.01233471196963953</v>
+        <v>0.01233468490784029</v>
       </c>
       <c r="C11" s="1">
-        <v>-0.0005255917913045138</v>
+        <v>-0.0005256185093207577</v>
       </c>
       <c r="D11" s="1">
-        <v>-0.004492423755518282</v>
+        <v>-0.004492361480108786</v>
       </c>
       <c r="E11" s="1">
-        <v>-8.4222378336829e-05</v>
+        <v>-8.425897270458726e-05</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -319,16 +319,16 @@
         </is>
       </c>
       <c r="B12" s="1">
-        <v>0.05137457237664433</v>
+        <v>0.05137458803333295</v>
       </c>
       <c r="C12" s="1">
-        <v>0.04387198797901926</v>
+        <v>0.04387200352398146</v>
       </c>
       <c r="D12" s="1">
-        <v>0.03904012344334129</v>
+        <v>0.0390401467549859</v>
       </c>
       <c r="E12" s="1">
-        <v>0.04441026948312721</v>
+        <v>0.04441028407914871</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -343,16 +343,16 @@
         </is>
       </c>
       <c r="B13" s="1">
-        <v>0.0711190385970919</v>
+        <v>0.07111902299004935</v>
       </c>
       <c r="C13" s="1">
-        <v>0.06420613273027009</v>
+        <v>0.06420611722395497</v>
       </c>
       <c r="D13" s="1">
-        <v>0.07878099979019582</v>
+        <v>0.07878097639576698</v>
       </c>
       <c r="E13" s="1">
-        <v>0.06259109955039022</v>
+        <v>0.06259108499995025</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -435,7 +435,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2313e90ebeaab0efd698b861dfa32462509b8eda4e8a4d82f6c81e003f867453</t>
+          <t>443ec5cb9bae85f19f38c97a291c62b4c61396997a6c8b51d774a47a10c3c5dd</t>
         </is>
       </c>
     </row>

--- a/public/data/systems/pds/public_recent_12m_returns.xlsx
+++ b/public/data/systems/pds/public_recent_12m_returns.xlsx
@@ -79,10 +79,10 @@
         </is>
       </c>
       <c r="B2" s="1">
-        <v>0.02712989058195125</v>
+        <v>0.0271298905819517</v>
       </c>
       <c r="C2" s="1">
-        <v>0.0495927392397908</v>
+        <v>0.04959273923979102</v>
       </c>
       <c r="D2" s="1">
         <v>0.09694349643809308</v>
@@ -103,16 +103,16 @@
         </is>
       </c>
       <c r="B3" s="1">
-        <v>-0.05362583562908274</v>
+        <v>-0.05362583805868504</v>
       </c>
       <c r="C3" s="1">
-        <v>-0.04612361638872287</v>
+        <v>-0.04612361883758587</v>
       </c>
       <c r="D3" s="1">
-        <v>-0.07173190949844122</v>
+        <v>-0.07173190909030314</v>
       </c>
       <c r="E3" s="1">
-        <v>-0.04327051870610032</v>
+        <v>-0.04327052147254551</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -127,16 +127,16 @@
         </is>
       </c>
       <c r="B4" s="1">
-        <v>-0.004646285493852487</v>
+        <v>-0.004646287235373192</v>
       </c>
       <c r="C4" s="1">
-        <v>-0.02181115625081043</v>
+        <v>-0.02181115796229849</v>
       </c>
       <c r="D4" s="1">
-        <v>-0.03191398347322494</v>
+        <v>-0.03191396317529782</v>
       </c>
       <c r="E4" s="1">
-        <v>-0.02069779542340811</v>
+        <v>-0.02069779959084606</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -151,16 +151,16 @@
         </is>
       </c>
       <c r="B5" s="1">
-        <v>0.07262416433683305</v>
+        <v>0.07262416829252172</v>
       </c>
       <c r="C5" s="1">
-        <v>0.06520330884225745</v>
+        <v>0.06520331277057889</v>
       </c>
       <c r="D5" s="1">
         <v>0.0824134496686979</v>
       </c>
       <c r="E5" s="1">
-        <v>0.06328151815016958</v>
+        <v>0.06328152250845975</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -175,16 +175,16 @@
         </is>
       </c>
       <c r="B6" s="1">
-        <v>0.07408961995335295</v>
+        <v>0.07408960677899024</v>
       </c>
       <c r="C6" s="1">
-        <v>0.08482852129814389</v>
+        <v>0.0848285079920621</v>
       </c>
       <c r="D6" s="1">
-        <v>0.1379985751862309</v>
+        <v>0.1379985472683445</v>
       </c>
       <c r="E6" s="1">
-        <v>0.07894709005298495</v>
+        <v>0.07894707822403269</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -199,16 +199,16 @@
         </is>
       </c>
       <c r="B7" s="1">
-        <v>-0.05020756333672527</v>
+        <v>-0.05020755386526954</v>
       </c>
       <c r="C7" s="1">
-        <v>-0.07289479718032899</v>
+        <v>-0.07289478793511384</v>
       </c>
       <c r="D7" s="1">
-        <v>-0.08649242053283257</v>
+        <v>-0.08649241529201013</v>
       </c>
       <c r="E7" s="1">
-        <v>-0.07137571863596992</v>
+        <v>-0.0713757089884629</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -223,16 +223,16 @@
         </is>
       </c>
       <c r="B8" s="1">
-        <v>0.058301239724311</v>
+        <v>0.05830123931052822</v>
       </c>
       <c r="C8" s="1">
-        <v>0.05724477273177775</v>
+        <v>0.05724477231840841</v>
       </c>
       <c r="D8" s="1">
-        <v>0.02882604470432648</v>
+        <v>0.02882606606117388</v>
       </c>
       <c r="E8" s="1">
-        <v>0.06040569511254956</v>
+        <v>0.06040569232533044</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -247,16 +247,16 @@
         </is>
       </c>
       <c r="B9" s="1">
-        <v>0.07233921421960976</v>
+        <v>0.07233919480074058</v>
       </c>
       <c r="C9" s="1">
-        <v>0.07604032030799313</v>
+        <v>0.07604030082210067</v>
       </c>
       <c r="D9" s="1">
-        <v>0.06981909532256569</v>
+        <v>0.06981909476860948</v>
       </c>
       <c r="E9" s="1">
-        <v>0.07672066252334653</v>
+        <v>0.07672064092950848</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -271,16 +271,16 @@
         </is>
       </c>
       <c r="B10" s="1">
-        <v>0.01089759907241317</v>
+        <v>0.01089763033967572</v>
       </c>
       <c r="C10" s="1">
-        <v>0.01931121044861328</v>
+        <v>0.019311241976111</v>
       </c>
       <c r="D10" s="1">
-        <v>0.02426733085800836</v>
+        <v>0.02426739669955946</v>
       </c>
       <c r="E10" s="1">
-        <v>0.01875737896088747</v>
+        <v>0.01875740666285353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -295,16 +295,16 @@
         </is>
       </c>
       <c r="B11" s="1">
-        <v>0.01233468490784029</v>
+        <v>0.01233467141657019</v>
       </c>
       <c r="C11" s="1">
-        <v>-0.0005256185093207577</v>
+        <v>-0.0005256318292036211</v>
       </c>
       <c r="D11" s="1">
-        <v>-0.004492361480108786</v>
+        <v>-0.004492432714165662</v>
       </c>
       <c r="E11" s="1">
-        <v>-8.425897270458726e-05</v>
+        <v>-8.426583887655159e-05</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -319,16 +319,16 @@
         </is>
       </c>
       <c r="B12" s="1">
-        <v>0.05137458803333295</v>
+        <v>0.05137458600050571</v>
       </c>
       <c r="C12" s="1">
-        <v>0.04387200352398146</v>
+        <v>0.04387200150566239</v>
       </c>
       <c r="D12" s="1">
-        <v>0.0390401467549859</v>
+        <v>0.03904007101155815</v>
       </c>
       <c r="E12" s="1">
-        <v>0.04441028407914871</v>
+        <v>0.04441029033640898</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -343,16 +343,16 @@
         </is>
       </c>
       <c r="B13" s="1">
-        <v>0.07111902299004935</v>
+        <v>0.0711190652514726</v>
       </c>
       <c r="C13" s="1">
-        <v>0.06420611722395497</v>
+        <v>0.06420615921262596</v>
       </c>
       <c r="D13" s="1">
-        <v>0.07878097639576698</v>
+        <v>0.07878105572185334</v>
       </c>
       <c r="E13" s="1">
-        <v>0.06259108499995025</v>
+        <v>0.06259112277554513</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -435,7 +435,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>443ec5cb9bae85f19f38c97a291c62b4c61396997a6c8b51d774a47a10c3c5dd</t>
+          <t>c478a510ae4c5a432e8905b648c10114a17734e99d43526b6eebe0b4e604c3ca</t>
         </is>
       </c>
     </row>

--- a/public/data/systems/pds/public_recent_12m_returns.xlsx
+++ b/public/data/systems/pds/public_recent_12m_returns.xlsx
@@ -79,16 +79,16 @@
         </is>
       </c>
       <c r="B2" s="1">
-        <v>0.0271298905819517</v>
+        <v>0.02712988572772002</v>
       </c>
       <c r="C2" s="1">
-        <v>0.04959273923979102</v>
+        <v>0.04959273427940025</v>
       </c>
       <c r="D2" s="1">
         <v>0.09694349643809308</v>
       </c>
       <c r="E2" s="1">
-        <v>0.04437253329281998</v>
+        <v>0.0443725278227789</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -103,16 +103,16 @@
         </is>
       </c>
       <c r="B3" s="1">
-        <v>-0.05362583805868504</v>
+        <v>-0.05362583375965835</v>
       </c>
       <c r="C3" s="1">
-        <v>-0.04612361883758587</v>
+        <v>-0.04612361450447933</v>
       </c>
       <c r="D3" s="1">
-        <v>-0.07173190909030314</v>
+        <v>-0.07173190949844122</v>
       </c>
       <c r="E3" s="1">
-        <v>-0.04327052147254551</v>
+        <v>-0.04327051661490966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -127,16 +127,16 @@
         </is>
       </c>
       <c r="B4" s="1">
-        <v>-0.004646287235373192</v>
+        <v>-0.00464629186732346</v>
       </c>
       <c r="C4" s="1">
-        <v>-0.02181115796229849</v>
+        <v>-0.02181116251437121</v>
       </c>
       <c r="D4" s="1">
-        <v>-0.03191396317529782</v>
+        <v>-0.03191398347322494</v>
       </c>
       <c r="E4" s="1">
-        <v>-0.02069779959084606</v>
+        <v>-0.02069780242053443</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -151,16 +151,16 @@
         </is>
       </c>
       <c r="B5" s="1">
-        <v>0.07262416829252172</v>
+        <v>0.07262415211783169</v>
       </c>
       <c r="C5" s="1">
-        <v>0.06520331277057889</v>
+        <v>0.0652032967077929</v>
       </c>
       <c r="D5" s="1">
         <v>0.0824134496686979</v>
       </c>
       <c r="E5" s="1">
-        <v>0.06328152250845975</v>
+        <v>0.06328150467900318</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -175,16 +175,16 @@
         </is>
       </c>
       <c r="B6" s="1">
-        <v>0.07408960677899024</v>
+        <v>0.07408960562991429</v>
       </c>
       <c r="C6" s="1">
-        <v>0.0848285079920621</v>
+        <v>0.08482850683149668</v>
       </c>
       <c r="D6" s="1">
-        <v>0.1379985472683445</v>
+        <v>0.1379985750292672</v>
       </c>
       <c r="E6" s="1">
-        <v>0.07894707822403269</v>
+        <v>0.0789470739632141</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -199,16 +199,16 @@
         </is>
       </c>
       <c r="B7" s="1">
-        <v>-0.05020755386526954</v>
+        <v>-0.05020755442328095</v>
       </c>
       <c r="C7" s="1">
-        <v>-0.07289478793511384</v>
+        <v>-0.07289478847979602</v>
       </c>
       <c r="D7" s="1">
-        <v>-0.08649241529201013</v>
+        <v>-0.08649243828879749</v>
       </c>
       <c r="E7" s="1">
-        <v>-0.0713757089884629</v>
+        <v>-0.07137570704106877</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -223,16 +223,16 @@
         </is>
       </c>
       <c r="B8" s="1">
-        <v>0.05830123931052822</v>
+        <v>0.05830124380383883</v>
       </c>
       <c r="C8" s="1">
-        <v>0.05724477231840841</v>
+        <v>0.05724477680723261</v>
       </c>
       <c r="D8" s="1">
-        <v>0.02882606606117388</v>
+        <v>0.02882604458055571</v>
       </c>
       <c r="E8" s="1">
-        <v>0.06040569232533044</v>
+        <v>0.06040569973418375</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -247,16 +247,16 @@
         </is>
       </c>
       <c r="B9" s="1">
-        <v>0.07233919480074058</v>
+        <v>0.07233919066819405</v>
       </c>
       <c r="C9" s="1">
-        <v>0.07604030082210067</v>
+        <v>0.076040296675292</v>
       </c>
       <c r="D9" s="1">
-        <v>0.06981909476860948</v>
+        <v>0.06981911828349796</v>
       </c>
       <c r="E9" s="1">
-        <v>0.07672064092950848</v>
+        <v>0.07672063372953142</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -271,16 +271,16 @@
         </is>
       </c>
       <c r="B10" s="1">
-        <v>0.01089763033967572</v>
+        <v>0.01089762537233852</v>
       </c>
       <c r="C10" s="1">
-        <v>0.019311241976111</v>
+        <v>0.01931123696743087</v>
       </c>
       <c r="D10" s="1">
-        <v>0.02426739669955946</v>
+        <v>0.0242673542185623</v>
       </c>
       <c r="E10" s="1">
-        <v>0.01875740666285353</v>
+        <v>0.01875740585834462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -295,16 +295,16 @@
         </is>
       </c>
       <c r="B11" s="1">
-        <v>0.01233467141657019</v>
+        <v>0.012334675655709</v>
       </c>
       <c r="C11" s="1">
-        <v>-0.0005256318292036211</v>
+        <v>-0.0005256276439172813</v>
       </c>
       <c r="D11" s="1">
-        <v>-0.004492432714165662</v>
+        <v>-0.004492438111519559</v>
       </c>
       <c r="E11" s="1">
-        <v>-8.426583887655159e-05</v>
+        <v>-8.426060952704262e-05</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -319,16 +319,16 @@
         </is>
       </c>
       <c r="B12" s="1">
-        <v>0.05137458600050571</v>
+        <v>0.05137459786067322</v>
       </c>
       <c r="C12" s="1">
-        <v>0.04387200150566239</v>
+        <v>0.0438720132811945</v>
       </c>
       <c r="D12" s="1">
-        <v>0.03904007101155815</v>
+        <v>0.03904016991470582</v>
       </c>
       <c r="E12" s="1">
-        <v>0.04441029033640898</v>
+        <v>0.04441029235671623</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -343,16 +343,16 @@
         </is>
       </c>
       <c r="B13" s="1">
-        <v>0.0711190652514726</v>
+        <v>0.07111903905848416</v>
       </c>
       <c r="C13" s="1">
-        <v>0.06420615921262596</v>
+        <v>0.06420613318868473</v>
       </c>
       <c r="D13" s="1">
-        <v>0.07878105572185334</v>
+        <v>0.07878097556647545</v>
       </c>
       <c r="E13" s="1">
-        <v>0.06259112277554513</v>
+        <v>0.0625911027487136</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -435,7 +435,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>c478a510ae4c5a432e8905b648c10114a17734e99d43526b6eebe0b4e604c3ca</t>
+          <t>8eaa8d88be711efdb699b1f43fd1ef7e3604c6e9f08ee957e7bd4555dcb4b230</t>
         </is>
       </c>
     </row>

--- a/public/data/systems/pds/public_recent_12m_returns.xlsx
+++ b/public/data/systems/pds/public_recent_12m_returns.xlsx
@@ -79,16 +79,16 @@
         </is>
       </c>
       <c r="B2" s="1">
-        <v>0.02712988572772002</v>
+        <v>0.02712989058195192</v>
       </c>
       <c r="C2" s="1">
-        <v>0.04959273427940025</v>
+        <v>0.04959273923979146</v>
       </c>
       <c r="D2" s="1">
         <v>0.09694349643809308</v>
       </c>
       <c r="E2" s="1">
-        <v>0.0443725278227789</v>
+        <v>0.0443725332928202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -103,16 +103,16 @@
         </is>
       </c>
       <c r="B3" s="1">
-        <v>-0.05362583375965835</v>
+        <v>-0.05362583563868684</v>
       </c>
       <c r="C3" s="1">
-        <v>-0.04612361450447933</v>
+        <v>-0.04612361639840334</v>
       </c>
       <c r="D3" s="1">
-        <v>-0.07173190949844122</v>
+        <v>-0.07173190963320608</v>
       </c>
       <c r="E3" s="1">
-        <v>-0.04327051661490966</v>
+        <v>-0.04327051870610121</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -127,16 +127,16 @@
         </is>
       </c>
       <c r="B4" s="1">
-        <v>-0.00464629186732346</v>
+        <v>-0.004646289828245553</v>
       </c>
       <c r="C4" s="1">
-        <v>-0.02181116251437121</v>
+        <v>-0.02181116051045717</v>
       </c>
       <c r="D4" s="1">
-        <v>-0.03191398347322494</v>
+        <v>-0.03191398450198579</v>
       </c>
       <c r="E4" s="1">
-        <v>-0.02069780242053443</v>
+        <v>-0.0206978001214505</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -151,16 +151,16 @@
         </is>
       </c>
       <c r="B5" s="1">
-        <v>0.07262415211783169</v>
+        <v>0.07262418352192013</v>
       </c>
       <c r="C5" s="1">
-        <v>0.0652032967077929</v>
+        <v>0.06520332789461514</v>
       </c>
       <c r="D5" s="1">
-        <v>0.0824134496686979</v>
+        <v>0.0824134747624814</v>
       </c>
       <c r="E5" s="1">
-        <v>0.06328150467900318</v>
+        <v>0.06328153658281077</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -175,16 +175,16 @@
         </is>
       </c>
       <c r="B6" s="1">
-        <v>0.07408960562991429</v>
+        <v>0.07408960506504769</v>
       </c>
       <c r="C6" s="1">
-        <v>0.08482850683149668</v>
+        <v>0.08482850626098259</v>
       </c>
       <c r="D6" s="1">
-        <v>0.1379985750292672</v>
+        <v>0.1379985658611249</v>
       </c>
       <c r="E6" s="1">
-        <v>0.0789470739632141</v>
+        <v>0.07894707426545433</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -199,16 +199,16 @@
         </is>
       </c>
       <c r="B7" s="1">
-        <v>-0.05020755442328095</v>
+        <v>-0.05020757291181344</v>
       </c>
       <c r="C7" s="1">
-        <v>-0.07289478847979602</v>
+        <v>-0.07289480652670188</v>
       </c>
       <c r="D7" s="1">
-        <v>-0.08649243828879749</v>
+        <v>-0.08649243834727849</v>
       </c>
       <c r="E7" s="1">
-        <v>-0.07137570704106877</v>
+        <v>-0.07137572706094109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -223,16 +223,16 @@
         </is>
       </c>
       <c r="B8" s="1">
-        <v>0.05830124380383883</v>
+        <v>0.05830125104439787</v>
       </c>
       <c r="C8" s="1">
-        <v>0.05724477680723261</v>
+        <v>0.05724478404056366</v>
       </c>
       <c r="D8" s="1">
-        <v>0.02882604458055571</v>
+        <v>0.02882604572689917</v>
       </c>
       <c r="E8" s="1">
-        <v>0.06040569973418375</v>
+        <v>0.06040570759188246</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -247,16 +247,16 @@
         </is>
       </c>
       <c r="B9" s="1">
-        <v>0.07233919066819405</v>
+        <v>0.0723392042660751</v>
       </c>
       <c r="C9" s="1">
-        <v>0.076040296675292</v>
+        <v>0.07604031032010483</v>
       </c>
       <c r="D9" s="1">
-        <v>0.06981911828349796</v>
+        <v>0.06981911730696955</v>
       </c>
       <c r="E9" s="1">
-        <v>0.07672063372953142</v>
+        <v>0.07672064895158703</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -271,16 +271,16 @@
         </is>
       </c>
       <c r="B10" s="1">
-        <v>0.01089762537233852</v>
+        <v>0.01089761524372745</v>
       </c>
       <c r="C10" s="1">
-        <v>0.01931123696743087</v>
+        <v>0.01931122675451991</v>
       </c>
       <c r="D10" s="1">
-        <v>0.0242673542185623</v>
+        <v>0.02426735290646387</v>
       </c>
       <c r="E10" s="1">
-        <v>0.01875740585834462</v>
+        <v>0.0187573945798496</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -295,16 +295,16 @@
         </is>
       </c>
       <c r="B11" s="1">
-        <v>0.012334675655709</v>
+        <v>0.01233468777366054</v>
       </c>
       <c r="C11" s="1">
-        <v>-0.0005256276439172813</v>
+        <v>-0.0005256156799069434</v>
       </c>
       <c r="D11" s="1">
-        <v>-0.004492438111519559</v>
+        <v>-0.004492360168281584</v>
       </c>
       <c r="E11" s="1">
-        <v>-8.426060952704262e-05</v>
+        <v>-8.425598674322021e-05</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -319,16 +319,16 @@
         </is>
       </c>
       <c r="B12" s="1">
-        <v>0.05137459786067322</v>
+        <v>0.05137459931852018</v>
       </c>
       <c r="C12" s="1">
-        <v>0.0438720132811945</v>
+        <v>0.04387201472863977</v>
       </c>
       <c r="D12" s="1">
-        <v>0.03904016991470582</v>
+        <v>0.03904009843898981</v>
       </c>
       <c r="E12" s="1">
-        <v>0.04441029235671623</v>
+        <v>0.04441030202545226</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -343,16 +343,16 @@
         </is>
       </c>
       <c r="B13" s="1">
-        <v>0.07111903905848416</v>
+        <v>0.07111900991168452</v>
       </c>
       <c r="C13" s="1">
-        <v>0.06420613318868473</v>
+        <v>0.06420610422999595</v>
       </c>
       <c r="D13" s="1">
-        <v>0.07878097556647545</v>
+        <v>0.07878102835139855</v>
       </c>
       <c r="E13" s="1">
-        <v>0.0625911027487136</v>
+        <v>0.06259106479621912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -435,7 +435,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>8eaa8d88be711efdb699b1f43fd1ef7e3604c6e9f08ee957e7bd4555dcb4b230</t>
+          <t>ab49fcdd582831c2ec57f68a64594ff83ecb12e58543decab429aba022f79028</t>
         </is>
       </c>
     </row>

--- a/public/data/systems/pds/public_recent_12m_returns.xlsx
+++ b/public/data/systems/pds/public_recent_12m_returns.xlsx
@@ -75,20 +75,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="B2" s="1">
-        <v>0.02712989058195192</v>
+        <v>-0.01111274483378177</v>
       </c>
       <c r="C2" s="1">
-        <v>0.04959273923979146</v>
+        <v>-0.004965604132446844</v>
       </c>
       <c r="D2" s="1">
-        <v>0.09694349643809308</v>
+        <v>-0.0007589648480446076</v>
       </c>
       <c r="E2" s="1">
-        <v>0.0443725332928202</v>
+        <v>-0.005403612272785407</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -99,20 +99,20 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B3" s="1">
-        <v>-0.05362583563868684</v>
+        <v>0.02712988572772002</v>
       </c>
       <c r="C3" s="1">
-        <v>-0.04612361639840334</v>
+        <v>0.04959273427940003</v>
       </c>
       <c r="D3" s="1">
-        <v>-0.07173190963320608</v>
+        <v>0.09694349643809308</v>
       </c>
       <c r="E3" s="1">
-        <v>-0.04327051870610121</v>
+        <v>0.04437252782277845</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -123,20 +123,20 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B4" s="1">
-        <v>-0.004646289828245553</v>
+        <v>-0.05362582685244532</v>
       </c>
       <c r="C4" s="1">
-        <v>-0.02181116051045717</v>
+        <v>-0.04612360754251066</v>
       </c>
       <c r="D4" s="1">
-        <v>-0.03191398450198579</v>
+        <v>-0.07173190949844122</v>
       </c>
       <c r="E4" s="1">
-        <v>-0.0206978001214505</v>
+        <v>-0.04327050886513684</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -147,20 +147,20 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="B5" s="1">
-        <v>0.07262418352192013</v>
+        <v>-0.004646297465385807</v>
       </c>
       <c r="C5" s="1">
-        <v>0.06520332789461514</v>
+        <v>-0.02181116801589411</v>
       </c>
       <c r="D5" s="1">
-        <v>0.0824134747624814</v>
+        <v>-0.03191398347322494</v>
       </c>
       <c r="E5" s="1">
-        <v>0.06328153658281077</v>
+        <v>-0.02069780846769864</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -171,20 +171,20 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="B6" s="1">
-        <v>0.07408960506504769</v>
+        <v>0.07262416223090673</v>
       </c>
       <c r="C6" s="1">
-        <v>0.08482850626098259</v>
+        <v>0.06520330675090036</v>
       </c>
       <c r="D6" s="1">
-        <v>0.1379985658611249</v>
+        <v>0.08241344964800246</v>
       </c>
       <c r="E6" s="1">
-        <v>0.07894707426545433</v>
+        <v>0.06328151577409469</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -195,20 +195,20 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="B7" s="1">
-        <v>-0.05020757291181344</v>
+        <v>0.07408962987286616</v>
       </c>
       <c r="C7" s="1">
-        <v>-0.07289480652670188</v>
+        <v>0.08482853131683354</v>
       </c>
       <c r="D7" s="1">
-        <v>-0.08649243834727849</v>
+        <v>0.1379985924679155</v>
       </c>
       <c r="E7" s="1">
-        <v>-0.07137572706094109</v>
+        <v>0.0789470992472503</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -219,20 +219,20 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B8" s="1">
-        <v>0.05830125104439787</v>
+        <v>-0.05020756233427126</v>
       </c>
       <c r="C8" s="1">
-        <v>0.05724478404056366</v>
+        <v>-0.0728947962018206</v>
       </c>
       <c r="D8" s="1">
-        <v>0.02882604572689917</v>
+        <v>-0.08649243781180949</v>
       </c>
       <c r="E8" s="1">
-        <v>0.06040570759188246</v>
+        <v>-0.0713757156487772</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -243,20 +243,20 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B9" s="1">
-        <v>0.0723392042660751</v>
+        <v>0.05830124719889662</v>
       </c>
       <c r="C9" s="1">
-        <v>0.07604031032010483</v>
+        <v>0.05724478019890156</v>
       </c>
       <c r="D9" s="1">
-        <v>0.06981911730696955</v>
+        <v>0.02882604353839802</v>
       </c>
       <c r="E9" s="1">
-        <v>0.07672064895158703</v>
+        <v>0.0604057035540233</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -267,20 +267,20 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="B10" s="1">
-        <v>0.01089761524372745</v>
+        <v>0.07233919967734503</v>
       </c>
       <c r="C10" s="1">
-        <v>0.01931122675451991</v>
+        <v>0.07604030571553699</v>
       </c>
       <c r="D10" s="1">
-        <v>0.02426735290646387</v>
+        <v>0.06981911926774353</v>
       </c>
       <c r="E10" s="1">
-        <v>0.0187573945798496</v>
+        <v>0.07672064358754849</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -291,20 +291,20 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="B11" s="1">
-        <v>0.01233468777366054</v>
+        <v>0.01089761741846296</v>
       </c>
       <c r="C11" s="1">
-        <v>-0.0005256156799069434</v>
+        <v>0.01931122894735582</v>
       </c>
       <c r="D11" s="1">
-        <v>-0.004492360168281584</v>
+        <v>0.02426741210635264</v>
       </c>
       <c r="E11" s="1">
-        <v>-8.425598674322021e-05</v>
+        <v>0.0187573905051357</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -315,20 +315,20 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="B12" s="1">
-        <v>0.05137459931852018</v>
+        <v>0.01233470622528765</v>
       </c>
       <c r="C12" s="1">
-        <v>0.04387201472863977</v>
+        <v>-0.0005255974626819926</v>
       </c>
       <c r="D12" s="1">
-        <v>0.03904009843898981</v>
+        <v>-0.004492443989537853</v>
       </c>
       <c r="E12" s="1">
-        <v>0.04441030202545226</v>
+        <v>-8.422640497451894e-05</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -339,20 +339,20 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="B13" s="1">
-        <v>0.07111900991168452</v>
+        <v>0.05137455570073035</v>
       </c>
       <c r="C13" s="1">
-        <v>0.06420610422999595</v>
+        <v>0.04387197142210386</v>
       </c>
       <c r="D13" s="1">
-        <v>0.07878102835139855</v>
+        <v>0.03904010031145222</v>
       </c>
       <c r="E13" s="1">
-        <v>0.06259106479621912</v>
+        <v>0.04441025370999707</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -435,7 +435,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ab49fcdd582831c2ec57f68a64594ff83ecb12e58543decab429aba022f79028</t>
+          <t>3c55d3799c34bfefbdeac4f0518ffed8647bdd0959c6785f6e02a8e49418c7c5</t>
         </is>
       </c>
     </row>

--- a/public/data/systems/pds/public_recent_12m_returns.xlsx
+++ b/public/data/systems/pds/public_recent_12m_returns.xlsx
@@ -79,10 +79,10 @@
         </is>
       </c>
       <c r="B2" s="1">
-        <v>-0.01111274483378177</v>
+        <v>-0.011112744833782</v>
       </c>
       <c r="C2" s="1">
-        <v>-0.004965604132446844</v>
+        <v>-0.004965604132447177</v>
       </c>
       <c r="D2" s="1">
         <v>-0.0007589648480446076</v>
@@ -103,16 +103,16 @@
         </is>
       </c>
       <c r="B3" s="1">
-        <v>0.02712988572772002</v>
+        <v>0.02712989058195148</v>
       </c>
       <c r="C3" s="1">
-        <v>0.04959273427940003</v>
+        <v>0.04959273923979124</v>
       </c>
       <c r="D3" s="1">
         <v>0.09694349643809308</v>
       </c>
       <c r="E3" s="1">
-        <v>0.04437252782277845</v>
+        <v>0.0443725332928202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -127,16 +127,16 @@
         </is>
       </c>
       <c r="B4" s="1">
-        <v>-0.05362582685244532</v>
+        <v>-0.0536258380537219</v>
       </c>
       <c r="C4" s="1">
-        <v>-0.04612360754251066</v>
+        <v>-0.0461236188325832</v>
       </c>
       <c r="D4" s="1">
-        <v>-0.07173190949844122</v>
+        <v>-0.07173190963320608</v>
       </c>
       <c r="E4" s="1">
-        <v>-0.04327050886513684</v>
+        <v>-0.0432705214174075</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -151,16 +151,16 @@
         </is>
       </c>
       <c r="B5" s="1">
-        <v>-0.004646297465385807</v>
+        <v>-0.004646289079214161</v>
       </c>
       <c r="C5" s="1">
-        <v>-0.02181116801589411</v>
+        <v>-0.02181115977434234</v>
       </c>
       <c r="D5" s="1">
-        <v>-0.03191398347322494</v>
+        <v>-0.03191398450198579</v>
       </c>
       <c r="E5" s="1">
-        <v>-0.02069780846769864</v>
+        <v>-0.02069779935794325</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -175,16 +175,16 @@
         </is>
       </c>
       <c r="B6" s="1">
-        <v>0.07262416223090673</v>
+        <v>0.0726241578818414</v>
       </c>
       <c r="C6" s="1">
-        <v>0.06520330675090036</v>
+        <v>0.06520330243192496</v>
       </c>
       <c r="D6" s="1">
-        <v>0.08241344964800246</v>
+        <v>0.08241347478317507</v>
       </c>
       <c r="E6" s="1">
-        <v>0.06328151577409469</v>
+        <v>0.06328150828753643</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -199,16 +199,16 @@
         </is>
       </c>
       <c r="B7" s="1">
-        <v>0.07408962987286616</v>
+        <v>0.07408961035902806</v>
       </c>
       <c r="C7" s="1">
-        <v>0.08482853131683354</v>
+        <v>0.08482851160789306</v>
       </c>
       <c r="D7" s="1">
-        <v>0.1379985924679155</v>
+        <v>0.1379985487015376</v>
       </c>
       <c r="E7" s="1">
-        <v>0.0789470992472503</v>
+        <v>0.07894708218362245</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -223,16 +223,16 @@
         </is>
       </c>
       <c r="B8" s="1">
-        <v>-0.05020756233427126</v>
+        <v>-0.05020756479928679</v>
       </c>
       <c r="C8" s="1">
-        <v>-0.0728947962018206</v>
+        <v>-0.07289479860795511</v>
       </c>
       <c r="D8" s="1">
-        <v>-0.08649243781180949</v>
+        <v>-0.08649241856845302</v>
       </c>
       <c r="E8" s="1">
-        <v>-0.0713757156487772</v>
+        <v>-0.0713757204034261</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -247,16 +247,16 @@
         </is>
       </c>
       <c r="B9" s="1">
-        <v>0.05830124719889662</v>
+        <v>0.0583012563057006</v>
       </c>
       <c r="C9" s="1">
-        <v>0.05724478019890156</v>
+        <v>0.05724478929661481</v>
       </c>
       <c r="D9" s="1">
-        <v>0.02882604353839802</v>
+        <v>0.0288260192584926</v>
       </c>
       <c r="E9" s="1">
-        <v>0.0604057035540233</v>
+        <v>0.06040571631134739</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -271,16 +271,16 @@
         </is>
       </c>
       <c r="B10" s="1">
-        <v>0.07233919967734503</v>
+        <v>0.07233917828300229</v>
       </c>
       <c r="C10" s="1">
-        <v>0.07604030571553699</v>
+        <v>0.07604028424735265</v>
       </c>
       <c r="D10" s="1">
-        <v>0.06981911926774353</v>
+        <v>0.06981911969031596</v>
       </c>
       <c r="E10" s="1">
-        <v>0.07672064358754849</v>
+        <v>0.07672061967543975</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -295,16 +295,16 @@
         </is>
       </c>
       <c r="B11" s="1">
-        <v>0.01089761741846296</v>
+        <v>0.01089762767379265</v>
       </c>
       <c r="C11" s="1">
-        <v>0.01931122894735582</v>
+        <v>0.01931123928803902</v>
       </c>
       <c r="D11" s="1">
-        <v>0.02426741210635264</v>
+        <v>0.02426737160455184</v>
       </c>
       <c r="E11" s="1">
-        <v>0.0187573905051357</v>
+        <v>0.01875740648746493</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -319,16 +319,16 @@
         </is>
       </c>
       <c r="B12" s="1">
-        <v>0.01233470622528765</v>
+        <v>0.01233469707596857</v>
       </c>
       <c r="C12" s="1">
-        <v>-0.0005255974626819926</v>
+        <v>-0.0005256064957710471</v>
       </c>
       <c r="D12" s="1">
-        <v>-0.004492443989537853</v>
+        <v>-0.004492417534770143</v>
       </c>
       <c r="E12" s="1">
-        <v>-8.422640497451894e-05</v>
+        <v>-8.423940496138371e-05</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -343,16 +343,16 @@
         </is>
       </c>
       <c r="B13" s="1">
-        <v>0.05137455570073035</v>
+        <v>0.05137457876963425</v>
       </c>
       <c r="C13" s="1">
-        <v>0.04387197142210386</v>
+        <v>0.04387199432638922</v>
       </c>
       <c r="D13" s="1">
-        <v>0.03904010031145222</v>
+        <v>0.03904009735066505</v>
       </c>
       <c r="E13" s="1">
-        <v>0.04441025370999707</v>
+        <v>0.04441027956645383</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -435,7 +435,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3c55d3799c34bfefbdeac4f0518ffed8647bdd0959c6785f6e02a8e49418c7c5</t>
+          <t>763fdc1fa23a1869b5701d8a5227bfce5e107153469fb3cf767aaa2bdf2b2f6a</t>
         </is>
       </c>
     </row>

--- a/public/data/systems/pds/public_recent_12m_returns.xlsx
+++ b/public/data/systems/pds/public_recent_12m_returns.xlsx
@@ -79,10 +79,10 @@
         </is>
       </c>
       <c r="B2" s="1">
-        <v>-0.011112744833782</v>
+        <v>-0.008810621195476043</v>
       </c>
       <c r="C2" s="1">
-        <v>-0.004965604132447177</v>
+        <v>-0.004965604132446844</v>
       </c>
       <c r="D2" s="1">
         <v>-0.0007589648480446076</v>
@@ -103,16 +103,16 @@
         </is>
       </c>
       <c r="B3" s="1">
-        <v>0.02712989058195148</v>
+        <v>0.02712988572771957</v>
       </c>
       <c r="C3" s="1">
-        <v>0.04959273923979124</v>
+        <v>0.04959273427939981</v>
       </c>
       <c r="D3" s="1">
         <v>0.09694349643809308</v>
       </c>
       <c r="E3" s="1">
-        <v>0.0443725332928202</v>
+        <v>0.04437252782277823</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -127,16 +127,16 @@
         </is>
       </c>
       <c r="B4" s="1">
-        <v>-0.0536258380537219</v>
+        <v>-0.0536258336120935</v>
       </c>
       <c r="C4" s="1">
-        <v>-0.0461236188325832</v>
+        <v>-0.0461236143557443</v>
       </c>
       <c r="D4" s="1">
         <v>-0.07173190963320608</v>
       </c>
       <c r="E4" s="1">
-        <v>-0.0432705214174075</v>
+        <v>-0.04327051643885116</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -151,16 +151,16 @@
         </is>
       </c>
       <c r="B5" s="1">
-        <v>-0.004646289079214161</v>
+        <v>-0.004646291136779834</v>
       </c>
       <c r="C5" s="1">
-        <v>-0.02181115977434234</v>
+        <v>-0.02181116179642617</v>
       </c>
       <c r="D5" s="1">
         <v>-0.03191398450198579</v>
       </c>
       <c r="E5" s="1">
-        <v>-0.02069779935794325</v>
+        <v>-0.02069780157259937</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -175,16 +175,16 @@
         </is>
       </c>
       <c r="B6" s="1">
-        <v>0.0726241578818414</v>
+        <v>0.07262419700908485</v>
       </c>
       <c r="C6" s="1">
-        <v>0.06520330243192496</v>
+        <v>0.06520334128846828</v>
       </c>
       <c r="D6" s="1">
-        <v>0.08241347478317507</v>
+        <v>0.0824134747624814</v>
       </c>
       <c r="E6" s="1">
-        <v>0.06328150828753643</v>
+        <v>0.06328155153368042</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -199,16 +199,16 @@
         </is>
       </c>
       <c r="B7" s="1">
-        <v>0.07408961035902806</v>
+        <v>0.07408960730631597</v>
       </c>
       <c r="C7" s="1">
-        <v>0.08482851160789306</v>
+        <v>0.0848285085246594</v>
       </c>
       <c r="D7" s="1">
-        <v>0.1379985487015376</v>
+        <v>0.1379985658611247</v>
       </c>
       <c r="E7" s="1">
-        <v>0.07894708218362245</v>
+        <v>0.0789470768017948</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -223,16 +223,16 @@
         </is>
       </c>
       <c r="B8" s="1">
-        <v>-0.05020756479928679</v>
+        <v>-0.05020756149826822</v>
       </c>
       <c r="C8" s="1">
-        <v>-0.07289479860795511</v>
+        <v>-0.07289479538578647</v>
       </c>
       <c r="D8" s="1">
-        <v>-0.08649241856845302</v>
+        <v>-0.08649241678884534</v>
       </c>
       <c r="E8" s="1">
-        <v>-0.0713757204034261</v>
+        <v>-0.07137571705724088</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -247,16 +247,16 @@
         </is>
       </c>
       <c r="B9" s="1">
-        <v>0.0583012563057006</v>
+        <v>0.05830123494959061</v>
       </c>
       <c r="C9" s="1">
-        <v>0.05724478929661481</v>
+        <v>0.05724476796182398</v>
       </c>
       <c r="D9" s="1">
-        <v>0.0288260192584926</v>
+        <v>0.02882599657686757</v>
       </c>
       <c r="E9" s="1">
-        <v>0.06040571631134739</v>
+        <v>0.06040569521942651</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -271,16 +271,16 @@
         </is>
       </c>
       <c r="B10" s="1">
-        <v>0.07233917828300229</v>
+        <v>0.07233920536141492</v>
       </c>
       <c r="C10" s="1">
-        <v>0.07604028424735265</v>
+        <v>0.07604031141922496</v>
       </c>
       <c r="D10" s="1">
-        <v>0.06981911969031596</v>
+        <v>0.06981914265124844</v>
       </c>
       <c r="E10" s="1">
-        <v>0.07672061967543975</v>
+        <v>0.07672064740238804</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -295,16 +295,16 @@
         </is>
       </c>
       <c r="B11" s="1">
-        <v>0.01089762767379265</v>
+        <v>0.01089758936166807</v>
       </c>
       <c r="C11" s="1">
-        <v>0.01931123928803902</v>
+        <v>0.01931120065704683</v>
       </c>
       <c r="D11" s="1">
-        <v>0.02426737160455184</v>
+        <v>0.02426736985069655</v>
       </c>
       <c r="E11" s="1">
-        <v>0.01875740648746493</v>
+        <v>0.01875736376713566</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -319,16 +319,16 @@
         </is>
       </c>
       <c r="B12" s="1">
-        <v>0.01233469707596857</v>
+        <v>0.0123347046564708</v>
       </c>
       <c r="C12" s="1">
-        <v>-0.0005256064957710471</v>
+        <v>-0.0005255990115692333</v>
       </c>
       <c r="D12" s="1">
-        <v>-0.004492417534770143</v>
+        <v>-0.004492400434754185</v>
       </c>
       <c r="E12" s="1">
-        <v>-8.423940496138371e-05</v>
+        <v>-8.423297721571466e-05</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -343,16 +343,16 @@
         </is>
       </c>
       <c r="B13" s="1">
-        <v>0.05137457876963425</v>
+        <v>0.05137460635265256</v>
       </c>
       <c r="C13" s="1">
-        <v>0.04387199432638922</v>
+        <v>0.04387202171257609</v>
       </c>
       <c r="D13" s="1">
-        <v>0.03904009735066505</v>
+        <v>0.03904009737601855</v>
       </c>
       <c r="E13" s="1">
-        <v>0.04441027956645383</v>
+        <v>0.04441030991669592</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -435,7 +435,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>763fdc1fa23a1869b5701d8a5227bfce5e107153469fb3cf767aaa2bdf2b2f6a</t>
+          <t>a4808898dd363ac231218b1a883a130995bc1fa5307e87dd616fcd4ee1961f44</t>
         </is>
       </c>
     </row>

--- a/public/data/systems/pds/public_recent_12m_returns.xlsx
+++ b/public/data/systems/pds/public_recent_12m_returns.xlsx
@@ -79,16 +79,16 @@
         </is>
       </c>
       <c r="B2" s="1">
-        <v>-0.008810621195476043</v>
+        <v>-0.008810622629181863</v>
       </c>
       <c r="C2" s="1">
-        <v>-0.004965604132446844</v>
+        <v>-0.004965605571713883</v>
       </c>
       <c r="D2" s="1">
         <v>-0.0007589648480446076</v>
       </c>
       <c r="E2" s="1">
-        <v>-0.005403612272785407</v>
+        <v>-0.005403613881671987</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -103,16 +103,16 @@
         </is>
       </c>
       <c r="B3" s="1">
-        <v>0.02712988572771957</v>
+        <v>0.02712988849967446</v>
       </c>
       <c r="C3" s="1">
-        <v>0.04959273427939981</v>
+        <v>0.04959273711197554</v>
       </c>
       <c r="D3" s="1">
         <v>0.09694349643809308</v>
       </c>
       <c r="E3" s="1">
-        <v>0.04437252782277823</v>
+        <v>0.04437253096333826</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -127,16 +127,16 @@
         </is>
       </c>
       <c r="B4" s="1">
-        <v>-0.0536258336120935</v>
+        <v>-0.05362583550962319</v>
       </c>
       <c r="C4" s="1">
-        <v>-0.0461236143557443</v>
+        <v>-0.04612361626831674</v>
       </c>
       <c r="D4" s="1">
-        <v>-0.07173190963320608</v>
+        <v>-0.07173190922506778</v>
       </c>
       <c r="E4" s="1">
-        <v>-0.04327051643885116</v>
+        <v>-0.04327051860622189</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -151,16 +151,16 @@
         </is>
       </c>
       <c r="B5" s="1">
-        <v>-0.004646291136779834</v>
+        <v>-0.004646289778039714</v>
       </c>
       <c r="C5" s="1">
-        <v>-0.02181116179642617</v>
+        <v>-0.02181116046111775</v>
       </c>
       <c r="D5" s="1">
-        <v>-0.03191398450198579</v>
+        <v>-0.03191396420405801</v>
       </c>
       <c r="E5" s="1">
-        <v>-0.02069780157259937</v>
+        <v>-0.02069780232993279</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -175,16 +175,16 @@
         </is>
       </c>
       <c r="B6" s="1">
-        <v>0.07262419700908485</v>
+        <v>0.07262418815945182</v>
       </c>
       <c r="C6" s="1">
-        <v>0.06520334128846828</v>
+        <v>0.06520333250006183</v>
       </c>
       <c r="D6" s="1">
-        <v>0.0824134747624814</v>
+        <v>0.08241347478317507</v>
       </c>
       <c r="E6" s="1">
-        <v>0.06328155153368042</v>
+        <v>0.06328154175100864</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -199,16 +199,16 @@
         </is>
       </c>
       <c r="B7" s="1">
-        <v>0.07408960730631597</v>
+        <v>0.07408959663445258</v>
       </c>
       <c r="C7" s="1">
-        <v>0.0848285085246594</v>
+        <v>0.08482849774609624</v>
       </c>
       <c r="D7" s="1">
-        <v>0.1379985658611247</v>
+        <v>0.1379985208185159</v>
       </c>
       <c r="E7" s="1">
-        <v>0.0789470768017948</v>
+        <v>0.07894706982477095</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -223,16 +223,16 @@
         </is>
       </c>
       <c r="B8" s="1">
-        <v>-0.05020756149826822</v>
+        <v>-0.05020755458311721</v>
       </c>
       <c r="C8" s="1">
-        <v>-0.07289479538578647</v>
+        <v>-0.07289478863581422</v>
       </c>
       <c r="D8" s="1">
-        <v>-0.08649241678884534</v>
+        <v>-0.08649239614649928</v>
       </c>
       <c r="E8" s="1">
-        <v>-0.07137571705724088</v>
+        <v>-0.07137571182882974</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -247,16 +247,16 @@
         </is>
       </c>
       <c r="B9" s="1">
-        <v>0.05830123494959061</v>
+        <v>0.05830126324772866</v>
       </c>
       <c r="C9" s="1">
-        <v>0.05724476796182398</v>
+        <v>0.05724479623171308</v>
       </c>
       <c r="D9" s="1">
-        <v>0.02882599657686757</v>
+        <v>0.02882601865798806</v>
       </c>
       <c r="E9" s="1">
-        <v>0.06040569521942651</v>
+        <v>0.06040572417765899</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -271,16 +271,16 @@
         </is>
       </c>
       <c r="B10" s="1">
-        <v>0.07233920536141492</v>
+        <v>0.07233918983286469</v>
       </c>
       <c r="C10" s="1">
-        <v>0.07604031141922496</v>
+        <v>0.07604029583707872</v>
       </c>
       <c r="D10" s="1">
-        <v>0.06981914265124844</v>
+        <v>0.06981911969031618</v>
       </c>
       <c r="E10" s="1">
-        <v>0.07672064740238804</v>
+        <v>0.07672063254408057</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -295,16 +295,16 @@
         </is>
       </c>
       <c r="B11" s="1">
-        <v>0.01089758936166807</v>
+        <v>0.01089761437700498</v>
       </c>
       <c r="C11" s="1">
-        <v>0.01931120065704683</v>
+        <v>0.01931122588058409</v>
       </c>
       <c r="D11" s="1">
-        <v>0.02426736985069655</v>
+        <v>0.02426738801647654</v>
       </c>
       <c r="E11" s="1">
-        <v>0.01875736376713566</v>
+        <v>0.0187573897814366</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -319,16 +319,16 @@
         </is>
       </c>
       <c r="B12" s="1">
-        <v>0.0123347046564708</v>
+        <v>0.01233469903074047</v>
       </c>
       <c r="C12" s="1">
-        <v>-0.0005255990115692333</v>
+        <v>-0.0005256045658321717</v>
       </c>
       <c r="D12" s="1">
-        <v>-0.004492400434754185</v>
+        <v>-0.004492458032090307</v>
       </c>
       <c r="E12" s="1">
-        <v>-8.423297721571466e-05</v>
+        <v>-8.423277482660918e-05</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -343,16 +343,16 @@
         </is>
       </c>
       <c r="B13" s="1">
-        <v>0.05137460635265256</v>
+        <v>0.0513745874931304</v>
       </c>
       <c r="C13" s="1">
-        <v>0.04387202171257609</v>
+        <v>0.04387200298763561</v>
       </c>
       <c r="D13" s="1">
-        <v>0.03904009737601855</v>
+        <v>0.03904012289338854</v>
       </c>
       <c r="E13" s="1">
-        <v>0.04441030991669592</v>
+        <v>0.04441028630113442</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -435,7 +435,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>a4808898dd363ac231218b1a883a130995bc1fa5307e87dd616fcd4ee1961f44</t>
+          <t>00701f90f8e5c19e598bc876605d06c1c745150cadeb48e85237b960588d33f7</t>
         </is>
       </c>
     </row>

--- a/public/data/systems/pds/public_recent_12m_returns.xlsx
+++ b/public/data/systems/pds/public_recent_12m_returns.xlsx
@@ -79,16 +79,16 @@
         </is>
       </c>
       <c r="B2" s="1">
-        <v>-0.008810622629181863</v>
+        <v>-0.008810631844592076</v>
       </c>
       <c r="C2" s="1">
-        <v>-0.004965605571713883</v>
+        <v>-0.004965614822872499</v>
       </c>
       <c r="D2" s="1">
         <v>-0.0007589648480446076</v>
       </c>
       <c r="E2" s="1">
-        <v>-0.005403613881671987</v>
+        <v>-0.005403624198249357</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -103,16 +103,16 @@
         </is>
       </c>
       <c r="B3" s="1">
-        <v>0.02712988849967446</v>
+        <v>0.02712989826731649</v>
       </c>
       <c r="C3" s="1">
-        <v>0.04959273711197554</v>
+        <v>0.0495927470932318</v>
       </c>
       <c r="D3" s="1">
         <v>0.09694349643809308</v>
       </c>
       <c r="E3" s="1">
-        <v>0.04437253096333826</v>
+        <v>0.04437254201335272</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -127,16 +127,16 @@
         </is>
       </c>
       <c r="B4" s="1">
-        <v>-0.05362583550962319</v>
+        <v>-0.05362583320748426</v>
       </c>
       <c r="C4" s="1">
-        <v>-0.04612361626831674</v>
+        <v>-0.04612361394792786</v>
       </c>
       <c r="D4" s="1">
-        <v>-0.07173190922506778</v>
+        <v>-0.07173190963320608</v>
       </c>
       <c r="E4" s="1">
-        <v>-0.04327051860622189</v>
+        <v>-0.04327051598086629</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -151,16 +151,16 @@
         </is>
       </c>
       <c r="B5" s="1">
-        <v>-0.004646289778039714</v>
+        <v>-0.004646290718342883</v>
       </c>
       <c r="C5" s="1">
-        <v>-0.02181116046111775</v>
+        <v>-0.02181116138520589</v>
       </c>
       <c r="D5" s="1">
-        <v>-0.03191396420405801</v>
+        <v>-0.03191398450198579</v>
       </c>
       <c r="E5" s="1">
-        <v>-0.02069780232993279</v>
+        <v>-0.02069780106894015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -175,16 +175,16 @@
         </is>
       </c>
       <c r="B6" s="1">
-        <v>0.07262418815945182</v>
+        <v>0.07262417501864826</v>
       </c>
       <c r="C6" s="1">
-        <v>0.06520333250006183</v>
+        <v>0.06520331945017088</v>
       </c>
       <c r="D6" s="1">
-        <v>0.08241347478317507</v>
+        <v>0.0824134747624814</v>
       </c>
       <c r="E6" s="1">
-        <v>0.06328154175100864</v>
+        <v>0.0632815271695859</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -199,16 +199,16 @@
         </is>
       </c>
       <c r="B7" s="1">
-        <v>0.07408959663445258</v>
+        <v>0.07408961879343345</v>
       </c>
       <c r="C7" s="1">
-        <v>0.08482849774609624</v>
+        <v>0.08482852012662612</v>
       </c>
       <c r="D7" s="1">
-        <v>0.1379985208185159</v>
+        <v>0.1379985660180871</v>
       </c>
       <c r="E7" s="1">
-        <v>0.07894706982477095</v>
+        <v>0.07894708970696596</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -223,16 +223,16 @@
         </is>
       </c>
       <c r="B8" s="1">
-        <v>-0.05020755458311721</v>
+        <v>-0.05020757363772466</v>
       </c>
       <c r="C8" s="1">
-        <v>-0.07289478863581422</v>
+        <v>-0.07289480723527375</v>
       </c>
       <c r="D8" s="1">
-        <v>-0.08649239614649928</v>
+        <v>-0.08649241856845302</v>
       </c>
       <c r="E8" s="1">
-        <v>-0.07137571182882974</v>
+        <v>-0.07137572999054242</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -247,16 +247,16 @@
         </is>
       </c>
       <c r="B9" s="1">
-        <v>0.05830126324772866</v>
+        <v>0.05830127831289378</v>
       </c>
       <c r="C9" s="1">
-        <v>0.05724479623171308</v>
+        <v>0.05724481128183889</v>
       </c>
       <c r="D9" s="1">
-        <v>0.02882601865798806</v>
+        <v>0.0288260192584926</v>
       </c>
       <c r="E9" s="1">
-        <v>0.06040572417765899</v>
+        <v>0.06040574080336358</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -271,16 +271,16 @@
         </is>
       </c>
       <c r="B10" s="1">
-        <v>0.07233918983286469</v>
+        <v>0.07233918540344098</v>
       </c>
       <c r="C10" s="1">
-        <v>0.07604029583707872</v>
+        <v>0.07604029139236723</v>
       </c>
       <c r="D10" s="1">
-        <v>0.06981911969031618</v>
+        <v>0.06981911926774331</v>
       </c>
       <c r="E10" s="1">
-        <v>0.07672063254408057</v>
+        <v>0.07672062764004828</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -295,16 +295,16 @@
         </is>
       </c>
       <c r="B11" s="1">
-        <v>0.01089761437700498</v>
+        <v>0.01089759143934743</v>
       </c>
       <c r="C11" s="1">
-        <v>0.01931122588058409</v>
+        <v>0.01931120275201814</v>
       </c>
       <c r="D11" s="1">
-        <v>0.02426738801647654</v>
+        <v>0.02426737969882309</v>
       </c>
       <c r="E11" s="1">
-        <v>0.0187573897814366</v>
+        <v>0.01875736496972547</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -319,16 +319,16 @@
         </is>
       </c>
       <c r="B12" s="1">
-        <v>0.01233469903074047</v>
+        <v>0.01233471345573922</v>
       </c>
       <c r="C12" s="1">
-        <v>-0.0005256045658321717</v>
+        <v>-0.0005255903240827253</v>
       </c>
       <c r="D12" s="1">
-        <v>-0.004492458032090307</v>
+        <v>-0.004492428821563088</v>
       </c>
       <c r="E12" s="1">
-        <v>-8.423277482660918e-05</v>
+        <v>-8.422018225773265e-05</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -343,16 +343,16 @@
         </is>
       </c>
       <c r="B13" s="1">
-        <v>0.0513745874931304</v>
+        <v>0.05137457726639671</v>
       </c>
       <c r="C13" s="1">
-        <v>0.04387200298763561</v>
+        <v>0.04387199283387955</v>
       </c>
       <c r="D13" s="1">
-        <v>0.03904012289338854</v>
+        <v>0.03904010040157457</v>
       </c>
       <c r="E13" s="1">
-        <v>0.04441028630113442</v>
+        <v>0.04441027752610283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -435,7 +435,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>00701f90f8e5c19e598bc876605d06c1c745150cadeb48e85237b960588d33f7</t>
+          <t>65b9c46d854f896f62e042c3873557eb2bffbe24d540df08a69b9d578622c812</t>
         </is>
       </c>
     </row>

--- a/public/data/systems/pds/public_recent_12m_returns.xlsx
+++ b/public/data/systems/pds/public_recent_12m_returns.xlsx
@@ -79,16 +79,16 @@
         </is>
       </c>
       <c r="B2" s="1">
-        <v>-0.008810631844592076</v>
+        <v>-0.008810620202306274</v>
       </c>
       <c r="C2" s="1">
-        <v>-0.004965614822872499</v>
+        <v>-0.004965603135423824</v>
       </c>
       <c r="D2" s="1">
         <v>-0.0007589648480446076</v>
       </c>
       <c r="E2" s="1">
-        <v>-0.005403624198249357</v>
+        <v>-0.005403611163649402</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -103,16 +103,16 @@
         </is>
       </c>
       <c r="B3" s="1">
-        <v>0.02712989826731649</v>
+        <v>0.02712988111382453</v>
       </c>
       <c r="C3" s="1">
-        <v>0.0495927470932318</v>
+        <v>0.04959272956460126</v>
       </c>
       <c r="D3" s="1">
         <v>0.09694349643809308</v>
       </c>
       <c r="E3" s="1">
-        <v>0.04437254201335272</v>
+        <v>0.04437252262037705</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -127,16 +127,16 @@
         </is>
       </c>
       <c r="B4" s="1">
-        <v>-0.05362583320748426</v>
+        <v>-0.05362583124684805</v>
       </c>
       <c r="C4" s="1">
-        <v>-0.04612361394792786</v>
+        <v>-0.0461236119717493</v>
       </c>
       <c r="D4" s="1">
         <v>-0.07173190963320608</v>
       </c>
       <c r="E4" s="1">
-        <v>-0.04327051598086629</v>
+        <v>-0.0432705137864402</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -151,16 +151,16 @@
         </is>
       </c>
       <c r="B5" s="1">
-        <v>-0.004646290718342883</v>
+        <v>-0.004646296586971022</v>
       </c>
       <c r="C5" s="1">
-        <v>-0.02181116138520589</v>
+        <v>-0.02181116715262899</v>
       </c>
       <c r="D5" s="1">
         <v>-0.03191398450198579</v>
       </c>
       <c r="E5" s="1">
-        <v>-0.02069780106894015</v>
+        <v>-0.0206978074956754</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -175,16 +175,16 @@
         </is>
       </c>
       <c r="B6" s="1">
-        <v>0.07262417501864826</v>
+        <v>0.07262419593765235</v>
       </c>
       <c r="C6" s="1">
-        <v>0.06520331945017088</v>
+        <v>0.06520334022444874</v>
       </c>
       <c r="D6" s="1">
         <v>0.0824134747624814</v>
       </c>
       <c r="E6" s="1">
-        <v>0.0632815271695859</v>
+        <v>0.06328155034303795</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -199,16 +199,16 @@
         </is>
       </c>
       <c r="B7" s="1">
-        <v>0.07408961879343345</v>
+        <v>0.07408959174332752</v>
       </c>
       <c r="C7" s="1">
-        <v>0.08482852012662612</v>
+        <v>0.08482849280607052</v>
       </c>
       <c r="D7" s="1">
-        <v>0.1379985660180871</v>
+        <v>0.1379985660180867</v>
       </c>
       <c r="E7" s="1">
-        <v>0.07894708970696596</v>
+        <v>0.07894705943836522</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -223,16 +223,16 @@
         </is>
       </c>
       <c r="B8" s="1">
-        <v>-0.05020757363772466</v>
+        <v>-0.05020756808553473</v>
       </c>
       <c r="C8" s="1">
-        <v>-0.07289480723527375</v>
+        <v>-0.07289480181570562</v>
       </c>
       <c r="D8" s="1">
-        <v>-0.08649241856845302</v>
+        <v>-0.08649244012688573</v>
       </c>
       <c r="E8" s="1">
-        <v>-0.07137572999054242</v>
+        <v>-0.07137572161330275</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -247,16 +247,16 @@
         </is>
       </c>
       <c r="B9" s="1">
-        <v>0.05830127831289378</v>
+        <v>0.05830127298525212</v>
       </c>
       <c r="C9" s="1">
-        <v>0.05724481128183889</v>
+        <v>0.05724480595951609</v>
       </c>
       <c r="D9" s="1">
-        <v>0.0288260192584926</v>
+        <v>0.02882606840852397</v>
       </c>
       <c r="E9" s="1">
-        <v>0.06040574080336358</v>
+        <v>0.06040572938077582</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -271,16 +271,16 @@
         </is>
       </c>
       <c r="B10" s="1">
-        <v>0.07233918540344098</v>
+        <v>0.07233919540698319</v>
       </c>
       <c r="C10" s="1">
-        <v>0.07604029139236723</v>
+        <v>0.07604030143043627</v>
       </c>
       <c r="D10" s="1">
-        <v>0.06981911926774331</v>
+        <v>0.06981909434603839</v>
       </c>
       <c r="E10" s="1">
-        <v>0.07672062764004828</v>
+        <v>0.07672064167799775</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -295,16 +295,16 @@
         </is>
       </c>
       <c r="B11" s="1">
-        <v>0.01089759143934743</v>
+        <v>0.01089762902148084</v>
       </c>
       <c r="C11" s="1">
-        <v>0.01931120275201814</v>
+        <v>0.01931124064694445</v>
       </c>
       <c r="D11" s="1">
-        <v>0.02426737969882309</v>
+        <v>0.02426737094431575</v>
       </c>
       <c r="E11" s="1">
-        <v>0.01875736496972547</v>
+        <v>0.01875740801466597</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -319,16 +319,16 @@
         </is>
       </c>
       <c r="B12" s="1">
-        <v>0.01233471345573922</v>
+        <v>0.01233467792001197</v>
       </c>
       <c r="C12" s="1">
-        <v>-0.0005255903240827253</v>
+        <v>-0.0005256254083786382</v>
       </c>
       <c r="D12" s="1">
-        <v>-0.004492428821563088</v>
+        <v>-0.004492396288130474</v>
       </c>
       <c r="E12" s="1">
-        <v>-8.422018225773265e-05</v>
+        <v>-8.42627813264496e-05</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -343,16 +343,16 @@
         </is>
       </c>
       <c r="B13" s="1">
-        <v>0.05137457726639671</v>
+        <v>0.05137457343183494</v>
       </c>
       <c r="C13" s="1">
-        <v>0.04387199283387955</v>
+        <v>0.04387198902668055</v>
       </c>
       <c r="D13" s="1">
-        <v>0.03904010040157457</v>
+        <v>0.03904010079664011</v>
       </c>
       <c r="E13" s="1">
-        <v>0.04441027752610283</v>
+        <v>0.04441027318151436</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -435,7 +435,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>65b9c46d854f896f62e042c3873557eb2bffbe24d540df08a69b9d578622c812</t>
+          <t>8b7f53bfd56c006b73feb0e2ebf90bff8836ba98fb3745d574493622af0b2e8e</t>
         </is>
       </c>
     </row>

--- a/public/data/systems/pds/public_recent_12m_returns.xlsx
+++ b/public/data/systems/pds/public_recent_12m_returns.xlsx
@@ -79,16 +79,16 @@
         </is>
       </c>
       <c r="B2" s="1">
-        <v>-0.008810620202306274</v>
+        <v>-0.008810631844592742</v>
       </c>
       <c r="C2" s="1">
-        <v>-0.004965603135423824</v>
+        <v>-0.004965614822872944</v>
       </c>
       <c r="D2" s="1">
         <v>-0.0007589648480446076</v>
       </c>
       <c r="E2" s="1">
-        <v>-0.005403611163649402</v>
+        <v>-0.005403624198249912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -103,16 +103,16 @@
         </is>
       </c>
       <c r="B3" s="1">
-        <v>0.02712988111382453</v>
+        <v>0.02712989826731715</v>
       </c>
       <c r="C3" s="1">
-        <v>0.04959272956460126</v>
+        <v>0.04959274709323247</v>
       </c>
       <c r="D3" s="1">
         <v>0.09694349643809308</v>
       </c>
       <c r="E3" s="1">
-        <v>0.04437252262037705</v>
+        <v>0.04437254201335317</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -127,16 +127,16 @@
         </is>
       </c>
       <c r="B4" s="1">
-        <v>-0.05362583124684805</v>
+        <v>-0.05362583564606294</v>
       </c>
       <c r="C4" s="1">
-        <v>-0.0461236119717493</v>
+        <v>-0.04612361640583773</v>
       </c>
       <c r="D4" s="1">
-        <v>-0.07173190963320608</v>
+        <v>-0.07173190922506778</v>
       </c>
       <c r="E4" s="1">
-        <v>-0.0432705137864402</v>
+        <v>-0.04327051875958676</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -151,16 +151,16 @@
         </is>
       </c>
       <c r="B5" s="1">
-        <v>-0.004646296586971022</v>
+        <v>-0.004646288261653142</v>
       </c>
       <c r="C5" s="1">
-        <v>-0.02181116715262899</v>
+        <v>-0.02181115897088071</v>
       </c>
       <c r="D5" s="1">
-        <v>-0.03191398450198579</v>
+        <v>-0.03191396420405801</v>
       </c>
       <c r="E5" s="1">
-        <v>-0.0206978074956754</v>
+        <v>-0.02069780067716198</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -175,16 +175,16 @@
         </is>
       </c>
       <c r="B6" s="1">
-        <v>0.07262419593765235</v>
+        <v>0.07262417047143144</v>
       </c>
       <c r="C6" s="1">
-        <v>0.06520334022444874</v>
+        <v>0.065203314934414</v>
       </c>
       <c r="D6" s="1">
         <v>0.0824134747624814</v>
       </c>
       <c r="E6" s="1">
-        <v>0.06328155034303795</v>
+        <v>0.06328152219097372</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -199,16 +199,16 @@
         </is>
       </c>
       <c r="B7" s="1">
-        <v>0.07408959174332752</v>
+        <v>0.0740896033778089</v>
       </c>
       <c r="C7" s="1">
-        <v>0.08482849280607052</v>
+        <v>0.08482850455687463</v>
       </c>
       <c r="D7" s="1">
-        <v>0.1379985660180867</v>
+        <v>0.1379985381350652</v>
       </c>
       <c r="E7" s="1">
-        <v>0.07894705943836522</v>
+        <v>0.07894707544264201</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -223,16 +223,16 @@
         </is>
       </c>
       <c r="B8" s="1">
-        <v>-0.05020756808553473</v>
+        <v>-0.05020755290302881</v>
       </c>
       <c r="C8" s="1">
-        <v>-0.07289480181570562</v>
+        <v>-0.07289478699585761</v>
       </c>
       <c r="D8" s="1">
-        <v>-0.08649244012688573</v>
+        <v>-0.08649241770493221</v>
       </c>
       <c r="E8" s="1">
-        <v>-0.07137572161330275</v>
+        <v>-0.07137570765239432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -247,16 +247,16 @@
         </is>
       </c>
       <c r="B9" s="1">
-        <v>0.05830127298525212</v>
+        <v>0.05830126117661005</v>
       </c>
       <c r="C9" s="1">
-        <v>0.05724480595951609</v>
+        <v>0.05724479416266171</v>
       </c>
       <c r="D9" s="1">
-        <v>0.02882606840852397</v>
+        <v>0.02882606780801966</v>
       </c>
       <c r="E9" s="1">
-        <v>0.06040572938077582</v>
+        <v>0.06040571638694425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -271,16 +271,16 @@
         </is>
       </c>
       <c r="B10" s="1">
-        <v>0.07233919540698319</v>
+        <v>0.07233918998135747</v>
       </c>
       <c r="C10" s="1">
-        <v>0.07604030143043627</v>
+        <v>0.07604029598608464</v>
       </c>
       <c r="D10" s="1">
-        <v>0.06981909434603839</v>
+        <v>0.06981909476861015</v>
       </c>
       <c r="E10" s="1">
-        <v>0.07672064167799775</v>
+        <v>0.07672063551914232</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -295,16 +295,16 @@
         </is>
       </c>
       <c r="B11" s="1">
-        <v>0.01089762902148084</v>
+        <v>0.01089762424030605</v>
       </c>
       <c r="C11" s="1">
-        <v>0.01931124064694445</v>
+        <v>0.01931123582597594</v>
       </c>
       <c r="D11" s="1">
-        <v>0.02426737094431575</v>
+        <v>0.02426735364537946</v>
       </c>
       <c r="E11" s="1">
-        <v>0.01875740801466597</v>
+        <v>0.01875740460181907</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -319,16 +319,16 @@
         </is>
       </c>
       <c r="B12" s="1">
-        <v>0.01233467792001197</v>
+        <v>0.01233469799939479</v>
       </c>
       <c r="C12" s="1">
-        <v>-0.0005256254083786382</v>
+        <v>-0.0005256055840758833</v>
       </c>
       <c r="D12" s="1">
-        <v>-0.004492396288130474</v>
+        <v>-0.004492337874092533</v>
       </c>
       <c r="E12" s="1">
-        <v>-8.42627813264496e-05</v>
+        <v>-8.424724561884034e-05</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -343,16 +343,16 @@
         </is>
       </c>
       <c r="B13" s="1">
-        <v>0.05137457343183494</v>
+        <v>0.05137456949676311</v>
       </c>
       <c r="C13" s="1">
-        <v>0.04387198902668055</v>
+        <v>0.04387198511968959</v>
       </c>
       <c r="D13" s="1">
-        <v>0.03904010079664011</v>
+        <v>0.03904007458601333</v>
       </c>
       <c r="E13" s="1">
-        <v>0.04441027318151436</v>
+        <v>0.04441027170614253</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -435,7 +435,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>8b7f53bfd56c006b73feb0e2ebf90bff8836ba98fb3745d574493622af0b2e8e</t>
+          <t>64fe5a18a43031e9b0eca7ceb8ec2aac5a822c91ab5ed941b7df6d8c568142fe</t>
         </is>
       </c>
     </row>

--- a/public/data/systems/pds/public_recent_12m_returns.xlsx
+++ b/public/data/systems/pds/public_recent_12m_returns.xlsx
@@ -79,16 +79,16 @@
         </is>
       </c>
       <c r="B2" s="1">
-        <v>-0.008810631844592742</v>
+        <v>-0.008810627081569211</v>
       </c>
       <c r="C2" s="1">
-        <v>-0.004965614822872944</v>
+        <v>-0.00496561004137297</v>
       </c>
       <c r="D2" s="1">
         <v>-0.0007589648480446076</v>
       </c>
       <c r="E2" s="1">
-        <v>-0.005403624198249912</v>
+        <v>-0.005403618863815907</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -103,16 +103,16 @@
         </is>
       </c>
       <c r="B3" s="1">
-        <v>0.02712989826731715</v>
+        <v>0.02712989333158444</v>
       </c>
       <c r="C3" s="1">
-        <v>0.04959274709323247</v>
+        <v>0.0495927420495581</v>
       </c>
       <c r="D3" s="1">
         <v>0.09694349643809308</v>
       </c>
       <c r="E3" s="1">
-        <v>0.04437254201335317</v>
+        <v>0.04437253641194827</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -127,16 +127,16 @@
         </is>
       </c>
       <c r="B4" s="1">
-        <v>-0.05362583564606294</v>
+        <v>-0.05362583117604935</v>
       </c>
       <c r="C4" s="1">
-        <v>-0.04612361640583773</v>
+        <v>-0.04612361190038883</v>
       </c>
       <c r="D4" s="1">
-        <v>-0.07173190922506778</v>
+        <v>-0.07173190949844122</v>
       </c>
       <c r="E4" s="1">
-        <v>-0.04327051875958676</v>
+        <v>-0.04327051371340951</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -151,16 +151,16 @@
         </is>
       </c>
       <c r="B5" s="1">
-        <v>-0.004646288261653142</v>
+        <v>-0.004646299505459695</v>
       </c>
       <c r="C5" s="1">
-        <v>-0.02181115897088071</v>
+        <v>-0.02181117002078836</v>
       </c>
       <c r="D5" s="1">
-        <v>-0.03191396420405801</v>
+        <v>-0.03191398347322494</v>
       </c>
       <c r="E5" s="1">
-        <v>-0.02069780067716198</v>
+        <v>-0.02069781072678312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -175,16 +175,16 @@
         </is>
       </c>
       <c r="B6" s="1">
-        <v>0.07262417047143144</v>
+        <v>0.0726241828326033</v>
       </c>
       <c r="C6" s="1">
-        <v>0.065203314934414</v>
+        <v>0.06520332721006605</v>
       </c>
       <c r="D6" s="1">
-        <v>0.0824134747624814</v>
+        <v>0.08241344964800246</v>
       </c>
       <c r="E6" s="1">
-        <v>0.06328152219097372</v>
+        <v>0.06328153857427443</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -199,16 +199,16 @@
         </is>
       </c>
       <c r="B7" s="1">
-        <v>0.0740896033778089</v>
+        <v>0.07408963655254741</v>
       </c>
       <c r="C7" s="1">
-        <v>0.08482850455687463</v>
+        <v>0.08482853806329915</v>
       </c>
       <c r="D7" s="1">
-        <v>0.1379985381350652</v>
+        <v>0.1379985924679155</v>
       </c>
       <c r="E7" s="1">
-        <v>0.07894707544264201</v>
+        <v>0.07894710666247362</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -223,16 +223,16 @@
         </is>
       </c>
       <c r="B8" s="1">
-        <v>-0.05020755290302881</v>
+        <v>-0.05020756543182048</v>
       </c>
       <c r="C8" s="1">
-        <v>-0.07289478699585761</v>
+        <v>-0.07289479922538011</v>
       </c>
       <c r="D8" s="1">
-        <v>-0.08649241770493221</v>
+        <v>-0.0864924377533316</v>
       </c>
       <c r="E8" s="1">
-        <v>-0.07137570765239432</v>
+        <v>-0.07137571902946105</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -247,16 +247,16 @@
         </is>
       </c>
       <c r="B9" s="1">
-        <v>0.05830126117661005</v>
+        <v>0.05830123841564627</v>
       </c>
       <c r="C9" s="1">
-        <v>0.05724479416266171</v>
+        <v>0.05724477142442019</v>
       </c>
       <c r="D9" s="1">
-        <v>0.02882606780801966</v>
+        <v>0.02882606726218251</v>
       </c>
       <c r="E9" s="1">
-        <v>0.06040571638694425</v>
+        <v>0.06040569113728633</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -271,16 +271,16 @@
         </is>
       </c>
       <c r="B10" s="1">
-        <v>0.07233918998135747</v>
+        <v>0.07233920205475797</v>
       </c>
       <c r="C10" s="1">
-        <v>0.07604029598608464</v>
+        <v>0.07604030810115536</v>
       </c>
       <c r="D10" s="1">
-        <v>0.06981909476861015</v>
+        <v>0.0698190947686097</v>
       </c>
       <c r="E10" s="1">
-        <v>0.07672063551914232</v>
+        <v>0.07672064901602993</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -295,16 +295,16 @@
         </is>
       </c>
       <c r="B11" s="1">
-        <v>0.01089762424030605</v>
+        <v>0.01089760996876543</v>
       </c>
       <c r="C11" s="1">
-        <v>0.01931123582597594</v>
+        <v>0.01931122143565411</v>
       </c>
       <c r="D11" s="1">
-        <v>0.02426735364537946</v>
+        <v>0.02426733729410357</v>
       </c>
       <c r="E11" s="1">
-        <v>0.01875740460181907</v>
+        <v>0.01875739045310709</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -319,16 +319,16 @@
         </is>
       </c>
       <c r="B12" s="1">
-        <v>0.01233469799939479</v>
+        <v>0.01233470410528836</v>
       </c>
       <c r="C12" s="1">
-        <v>-0.0005256055840758833</v>
+        <v>-0.0005255995557494897</v>
       </c>
       <c r="D12" s="1">
-        <v>-0.004492337874092533</v>
+        <v>-0.004492384104327951</v>
       </c>
       <c r="E12" s="1">
-        <v>-8.424724561884034e-05</v>
+        <v>-8.423541342161833e-05</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -343,16 +343,16 @@
         </is>
       </c>
       <c r="B13" s="1">
-        <v>0.05137456949676311</v>
+        <v>0.05137457081143748</v>
       </c>
       <c r="C13" s="1">
-        <v>0.04387198511968959</v>
+        <v>0.04387198642498191</v>
       </c>
       <c r="D13" s="1">
-        <v>0.03904007458601333</v>
+        <v>0.03904012271172408</v>
       </c>
       <c r="E13" s="1">
-        <v>0.04441027170614253</v>
+        <v>0.04441026775407897</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -435,7 +435,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>64fe5a18a43031e9b0eca7ceb8ec2aac5a822c91ab5ed941b7df6d8c568142fe</t>
+          <t>4eb3a01b6d076e0cf834bfe01fe7e47a38cd222cf2a933b1d2f8fbd30c238ce5</t>
         </is>
       </c>
     </row>

--- a/public/data/systems/pds/public_recent_12m_returns.xlsx
+++ b/public/data/systems/pds/public_recent_12m_returns.xlsx
@@ -79,16 +79,16 @@
         </is>
       </c>
       <c r="B2" s="1">
-        <v>-0.008810627081569211</v>
+        <v>-0.00881062981908165</v>
       </c>
       <c r="C2" s="1">
-        <v>-0.00496561004137297</v>
+        <v>-0.004965612789505136</v>
       </c>
       <c r="D2" s="1">
         <v>-0.0007589648480446076</v>
       </c>
       <c r="E2" s="1">
-        <v>-0.005403618863815907</v>
+        <v>-0.005403621934130354</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -103,16 +103,16 @@
         </is>
       </c>
       <c r="B3" s="1">
-        <v>0.02712989333158444</v>
+        <v>0.02712989595027926</v>
       </c>
       <c r="C3" s="1">
-        <v>0.0495927420495581</v>
+        <v>0.04959274472552133</v>
       </c>
       <c r="D3" s="1">
         <v>0.09694349643809308</v>
       </c>
       <c r="E3" s="1">
-        <v>0.04437253641194827</v>
+        <v>0.04437253941879304</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -127,16 +127,16 @@
         </is>
       </c>
       <c r="B4" s="1">
-        <v>-0.05362583117604935</v>
+        <v>-0.05362583541495314</v>
       </c>
       <c r="C4" s="1">
-        <v>-0.04612361190038883</v>
+        <v>-0.04612361617289606</v>
       </c>
       <c r="D4" s="1">
         <v>-0.07173190949844122</v>
       </c>
       <c r="E4" s="1">
-        <v>-0.04327051371340951</v>
+        <v>-0.04327051847318308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -151,16 +151,16 @@
         </is>
       </c>
       <c r="B5" s="1">
-        <v>-0.004646299505459695</v>
+        <v>-0.004646288921554276</v>
       </c>
       <c r="C5" s="1">
-        <v>-0.02181117002078836</v>
+        <v>-0.02181115961940194</v>
       </c>
       <c r="D5" s="1">
         <v>-0.03191398347322494</v>
       </c>
       <c r="E5" s="1">
-        <v>-0.02069781072678312</v>
+        <v>-0.02069779924898407</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -175,16 +175,16 @@
         </is>
       </c>
       <c r="B6" s="1">
-        <v>0.0726241828326033</v>
+        <v>0.07262415054408811</v>
       </c>
       <c r="C6" s="1">
-        <v>0.06520332721006605</v>
+        <v>0.06520329514493706</v>
       </c>
       <c r="D6" s="1">
-        <v>0.08241344964800246</v>
+        <v>0.0824134496686979</v>
       </c>
       <c r="E6" s="1">
-        <v>0.06328153857427443</v>
+        <v>0.06328150294265034</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -199,16 +199,16 @@
         </is>
       </c>
       <c r="B7" s="1">
-        <v>0.07408963655254741</v>
+        <v>0.07408961643461942</v>
       </c>
       <c r="C7" s="1">
-        <v>0.08482853806329915</v>
+        <v>0.08482851774422828</v>
       </c>
       <c r="D7" s="1">
-        <v>0.1379985924679155</v>
+        <v>0.1379985751513659</v>
       </c>
       <c r="E7" s="1">
-        <v>0.07894710666247362</v>
+        <v>0.07894708613506518</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -223,16 +223,16 @@
         </is>
       </c>
       <c r="B8" s="1">
-        <v>-0.05020756543182048</v>
+        <v>-0.05020755895794715</v>
       </c>
       <c r="C8" s="1">
-        <v>-0.07289479922538011</v>
+        <v>-0.07289479290614487</v>
       </c>
       <c r="D8" s="1">
-        <v>-0.0864924377533316</v>
+        <v>-0.08649241827623477</v>
       </c>
       <c r="E8" s="1">
-        <v>-0.07137571902946105</v>
+        <v>-0.07137571413491128</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -247,16 +247,16 @@
         </is>
       </c>
       <c r="B9" s="1">
-        <v>0.05830123841564627</v>
+        <v>0.0583012469580737</v>
       </c>
       <c r="C9" s="1">
-        <v>0.05724477142442019</v>
+        <v>0.05724477995831956</v>
       </c>
       <c r="D9" s="1">
-        <v>0.02882606726218251</v>
+        <v>0.02882602098054221</v>
       </c>
       <c r="E9" s="1">
-        <v>0.06040569113728633</v>
+        <v>0.06040570581749694</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -271,16 +271,16 @@
         </is>
       </c>
       <c r="B10" s="1">
-        <v>0.07233920205475797</v>
+        <v>0.07233920212387757</v>
       </c>
       <c r="C10" s="1">
-        <v>0.07604030810115536</v>
+        <v>0.07604030817051366</v>
       </c>
       <c r="D10" s="1">
-        <v>0.0698190947686097</v>
+        <v>0.06981911926774265</v>
       </c>
       <c r="E10" s="1">
-        <v>0.07672064901602993</v>
+        <v>0.07672064630705155</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -295,16 +295,16 @@
         </is>
       </c>
       <c r="B11" s="1">
-        <v>0.01089760996876543</v>
+        <v>0.0108976242830976</v>
       </c>
       <c r="C11" s="1">
-        <v>0.01931122143565411</v>
+        <v>0.01931123586912364</v>
       </c>
       <c r="D11" s="1">
-        <v>0.02426733729410357</v>
+        <v>0.02426739590103355</v>
       </c>
       <c r="E11" s="1">
-        <v>0.01875739045310709</v>
+        <v>0.01875739996760117</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -319,16 +319,16 @@
         </is>
       </c>
       <c r="B12" s="1">
-        <v>0.01233470410528836</v>
+        <v>0.01233467466570048</v>
       </c>
       <c r="C12" s="1">
-        <v>-0.0005255995557494897</v>
+        <v>-0.0005256286213485284</v>
       </c>
       <c r="D12" s="1">
-        <v>-0.004492384104327951</v>
+        <v>-0.004492450514982593</v>
       </c>
       <c r="E12" s="1">
-        <v>-8.423541342161833e-05</v>
+        <v>-8.426031798081102e-05</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -343,16 +343,16 @@
         </is>
       </c>
       <c r="B13" s="1">
-        <v>0.05137457081143748</v>
+        <v>0.05137458074939349</v>
       </c>
       <c r="C13" s="1">
-        <v>0.04387198642498191</v>
+        <v>0.04387199629202176</v>
       </c>
       <c r="D13" s="1">
-        <v>0.03904012271172408</v>
+        <v>0.03904012343175989</v>
       </c>
       <c r="E13" s="1">
-        <v>0.04441026775407897</v>
+        <v>0.04441027877794412</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -435,7 +435,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4eb3a01b6d076e0cf834bfe01fe7e47a38cd222cf2a933b1d2f8fbd30c238ce5</t>
+          <t>c6a938bd6ac1fdc4f5b900b82222f44782b6cd917026eb12bfb1b2756aae8c2e</t>
         </is>
       </c>
     </row>

--- a/public/data/systems/pds/public_recent_12m_returns.xlsx
+++ b/public/data/systems/pds/public_recent_12m_returns.xlsx
@@ -79,10 +79,10 @@
         </is>
       </c>
       <c r="B2" s="1">
-        <v>-0.00881062981908165</v>
+        <v>-0.008810629819081539</v>
       </c>
       <c r="C2" s="1">
-        <v>-0.004965612789505136</v>
+        <v>-0.004965612789504692</v>
       </c>
       <c r="D2" s="1">
         <v>-0.0007589648480446076</v>
@@ -103,16 +103,16 @@
         </is>
       </c>
       <c r="B3" s="1">
-        <v>0.02712989595027926</v>
+        <v>0.02712989595027904</v>
       </c>
       <c r="C3" s="1">
-        <v>0.04959274472552133</v>
+        <v>0.04959274472552111</v>
       </c>
       <c r="D3" s="1">
         <v>0.09694349643809308</v>
       </c>
       <c r="E3" s="1">
-        <v>0.04437253941879304</v>
+        <v>0.04437253941879327</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -127,16 +127,16 @@
         </is>
       </c>
       <c r="B4" s="1">
-        <v>-0.05362583541495314</v>
+        <v>-0.05362583564606327</v>
       </c>
       <c r="C4" s="1">
-        <v>-0.04612361617289606</v>
+        <v>-0.04612361640583851</v>
       </c>
       <c r="D4" s="1">
-        <v>-0.07173190949844122</v>
+        <v>-0.07173190922506778</v>
       </c>
       <c r="E4" s="1">
-        <v>-0.04327051847318308</v>
+        <v>-0.04327051875958676</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -151,16 +151,16 @@
         </is>
       </c>
       <c r="B5" s="1">
-        <v>-0.004646288921554276</v>
+        <v>-0.004646292480847136</v>
       </c>
       <c r="C5" s="1">
-        <v>-0.02181115961940194</v>
+        <v>-0.02181116311731557</v>
       </c>
       <c r="D5" s="1">
-        <v>-0.03191398347322494</v>
+        <v>-0.03191396420405801</v>
       </c>
       <c r="E5" s="1">
-        <v>-0.02069779924898407</v>
+        <v>-0.02069780529721954</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -175,16 +175,16 @@
         </is>
       </c>
       <c r="B6" s="1">
-        <v>0.07262415054408811</v>
+        <v>0.07262415074639317</v>
       </c>
       <c r="C6" s="1">
-        <v>0.06520329514493706</v>
+        <v>0.06520329534584213</v>
       </c>
       <c r="D6" s="1">
-        <v>0.0824134496686979</v>
+        <v>0.08241347478317507</v>
       </c>
       <c r="E6" s="1">
-        <v>0.06328150294265034</v>
+        <v>0.06328150036309066</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -199,16 +199,16 @@
         </is>
       </c>
       <c r="B7" s="1">
-        <v>0.07408961643461942</v>
+        <v>0.07408961693245164</v>
       </c>
       <c r="C7" s="1">
-        <v>0.08482851774422828</v>
+        <v>0.08482851824703941</v>
       </c>
       <c r="D7" s="1">
-        <v>0.1379985751513659</v>
+        <v>0.1379985208185159</v>
       </c>
       <c r="E7" s="1">
-        <v>0.07894708613506518</v>
+        <v>0.07894709250074139</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -223,16 +223,16 @@
         </is>
       </c>
       <c r="B8" s="1">
-        <v>-0.05020755895794715</v>
+        <v>-0.05020756728382214</v>
       </c>
       <c r="C8" s="1">
-        <v>-0.07289479290614487</v>
+        <v>-0.07289480103314361</v>
       </c>
       <c r="D8" s="1">
-        <v>-0.08649241827623477</v>
+        <v>-0.08649241766556526</v>
       </c>
       <c r="E8" s="1">
-        <v>-0.07137571413491128</v>
+        <v>-0.07137572324521058</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -247,16 +247,16 @@
         </is>
       </c>
       <c r="B9" s="1">
-        <v>0.0583012469580737</v>
+        <v>0.05830126396823343</v>
       </c>
       <c r="C9" s="1">
-        <v>0.05724477995831956</v>
+        <v>0.05724479695149776</v>
       </c>
       <c r="D9" s="1">
-        <v>0.02882602098054221</v>
+        <v>0.02882606720751824</v>
       </c>
       <c r="E9" s="1">
-        <v>0.06040570581749694</v>
+        <v>0.06040571956577234</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -271,16 +271,16 @@
         </is>
       </c>
       <c r="B10" s="1">
-        <v>0.07233920212387757</v>
+        <v>0.07233920974011454</v>
       </c>
       <c r="C10" s="1">
-        <v>0.07604030817051366</v>
+        <v>0.07604031581303694</v>
       </c>
       <c r="D10" s="1">
-        <v>0.06981911926774265</v>
+        <v>0.06981909434603817</v>
       </c>
       <c r="E10" s="1">
-        <v>0.07672064630705155</v>
+        <v>0.07672065763886193</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -295,16 +295,16 @@
         </is>
       </c>
       <c r="B11" s="1">
-        <v>0.0108976242830976</v>
+        <v>0.01089762161573171</v>
       </c>
       <c r="C11" s="1">
-        <v>0.01931123586912364</v>
+        <v>0.01931123317955841</v>
       </c>
       <c r="D11" s="1">
-        <v>0.02426739590103355</v>
+        <v>0.02426737107639099</v>
       </c>
       <c r="E11" s="1">
-        <v>0.01875739996760117</v>
+        <v>0.01875739971887569</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -319,16 +319,16 @@
         </is>
       </c>
       <c r="B12" s="1">
-        <v>0.01233467466570048</v>
+        <v>0.01233468965295748</v>
       </c>
       <c r="C12" s="1">
-        <v>-0.0005256286213485284</v>
+        <v>-0.0005256138244837949</v>
       </c>
       <c r="D12" s="1">
-        <v>-0.004492450514982593</v>
+        <v>-0.004492393640905257</v>
       </c>
       <c r="E12" s="1">
-        <v>-8.426031798081102e-05</v>
+        <v>-8.425019875235584e-05</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -343,16 +343,16 @@
         </is>
       </c>
       <c r="B13" s="1">
-        <v>0.05137458074939349</v>
+        <v>0.05137456621462233</v>
       </c>
       <c r="C13" s="1">
-        <v>0.04387199629202176</v>
+        <v>0.04387198186096963</v>
       </c>
       <c r="D13" s="1">
-        <v>0.03904012343175989</v>
+        <v>0.03904012127597367</v>
       </c>
       <c r="E13" s="1">
-        <v>0.04441027877794412</v>
+        <v>0.04441026285102501</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -435,7 +435,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>c6a938bd6ac1fdc4f5b900b82222f44782b6cd917026eb12bfb1b2756aae8c2e</t>
+          <t>56de3d51b4dc72f084a6addd878ba3850e32b193e20f126ef5cd6dd87c63f387</t>
         </is>
       </c>
     </row>

--- a/public/data/systems/pds/public_recent_12m_returns.xlsx
+++ b/public/data/systems/pds/public_recent_12m_returns.xlsx
@@ -79,16 +79,16 @@
         </is>
       </c>
       <c r="B2" s="1">
-        <v>-0.008810629819081539</v>
+        <v>-0.008810634271467555</v>
       </c>
       <c r="C2" s="1">
-        <v>-0.004965612789504692</v>
+        <v>-0.004965617259163002</v>
       </c>
       <c r="D2" s="1">
         <v>-0.0007589648480446076</v>
       </c>
       <c r="E2" s="1">
-        <v>-0.005403621934130354</v>
+        <v>-0.005403626916273052</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -103,16 +103,16 @@
         </is>
       </c>
       <c r="B3" s="1">
-        <v>0.02712989595027904</v>
+        <v>0.02712990078219013</v>
       </c>
       <c r="C3" s="1">
-        <v>0.04959274472552111</v>
+        <v>0.04959274966310478</v>
       </c>
       <c r="D3" s="1">
         <v>0.09694349643809308</v>
       </c>
       <c r="E3" s="1">
-        <v>0.04437253941879327</v>
+        <v>0.0443725448674035</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -127,16 +127,16 @@
         </is>
       </c>
       <c r="B4" s="1">
-        <v>-0.05362583564606327</v>
+        <v>-0.053625835409014</v>
       </c>
       <c r="C4" s="1">
-        <v>-0.04612361640583851</v>
+        <v>-0.04612361616690996</v>
       </c>
       <c r="D4" s="1">
-        <v>-0.07173190922506778</v>
+        <v>-0.07173190909030314</v>
       </c>
       <c r="E4" s="1">
-        <v>-0.04327051875958676</v>
+        <v>-0.04327051850581842</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -151,16 +151,16 @@
         </is>
       </c>
       <c r="B5" s="1">
-        <v>-0.004646292480847136</v>
+        <v>-0.00464628923241972</v>
       </c>
       <c r="C5" s="1">
-        <v>-0.02181116311731557</v>
+        <v>-0.02181115992490623</v>
       </c>
       <c r="D5" s="1">
-        <v>-0.03191396420405801</v>
+        <v>-0.03191396317529782</v>
       </c>
       <c r="E5" s="1">
-        <v>-0.02069780529721954</v>
+        <v>-0.02069780180194225</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -175,16 +175,16 @@
         </is>
       </c>
       <c r="B6" s="1">
-        <v>0.07262415074639317</v>
+        <v>0.07262418701623563</v>
       </c>
       <c r="C6" s="1">
-        <v>0.06520329534584213</v>
+        <v>0.06520333136475442</v>
       </c>
       <c r="D6" s="1">
-        <v>0.08241347478317507</v>
+        <v>0.08241344964800246</v>
       </c>
       <c r="E6" s="1">
-        <v>0.06328150036309066</v>
+        <v>0.06328154323856028</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -199,16 +199,16 @@
         </is>
       </c>
       <c r="B7" s="1">
-        <v>0.07408961693245164</v>
+        <v>0.07408960113147267</v>
       </c>
       <c r="C7" s="1">
-        <v>0.08482851824703941</v>
+        <v>0.08482850228807903</v>
       </c>
       <c r="D7" s="1">
-        <v>0.1379985208185159</v>
+        <v>0.1379985646197579</v>
       </c>
       <c r="E7" s="1">
-        <v>0.07894709250074139</v>
+        <v>0.07894707003310963</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -223,16 +223,16 @@
         </is>
       </c>
       <c r="B8" s="1">
-        <v>-0.05020756728382214</v>
+        <v>-0.05020755350718997</v>
       </c>
       <c r="C8" s="1">
-        <v>-0.07289480103314361</v>
+        <v>-0.07289478758558698</v>
       </c>
       <c r="D8" s="1">
-        <v>-0.08649241766556526</v>
+        <v>-0.08649241764645288</v>
       </c>
       <c r="E8" s="1">
-        <v>-0.07137572324521058</v>
+        <v>-0.07137570832534368</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -247,16 +247,16 @@
         </is>
       </c>
       <c r="B9" s="1">
-        <v>0.05830126396823343</v>
+        <v>0.05830126368003485</v>
       </c>
       <c r="C9" s="1">
-        <v>0.05724479695149776</v>
+        <v>0.05724479666358784</v>
       </c>
       <c r="D9" s="1">
-        <v>0.02882606720751824</v>
+        <v>0.02882606636797824</v>
       </c>
       <c r="E9" s="1">
-        <v>0.06040571956577234</v>
+        <v>0.06040571936923755</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -271,16 +271,16 @@
         </is>
       </c>
       <c r="B10" s="1">
-        <v>0.07233920974011454</v>
+        <v>0.07233918564662289</v>
       </c>
       <c r="C10" s="1">
-        <v>0.07604031581303694</v>
+        <v>0.07604029163638781</v>
       </c>
       <c r="D10" s="1">
-        <v>0.06981909434603817</v>
+        <v>0.06981909459080771</v>
       </c>
       <c r="E10" s="1">
-        <v>0.07672065763886193</v>
+        <v>0.07672063070510426</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -295,16 +295,16 @@
         </is>
       </c>
       <c r="B11" s="1">
-        <v>0.01089762161573171</v>
+        <v>0.01089762242039161</v>
       </c>
       <c r="C11" s="1">
-        <v>0.01931123317955841</v>
+        <v>0.01931123399091494</v>
       </c>
       <c r="D11" s="1">
-        <v>0.02426737107639099</v>
+        <v>0.02426739656437671</v>
       </c>
       <c r="E11" s="1">
-        <v>0.01875739971887569</v>
+        <v>0.01875739785041231</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -319,16 +319,16 @@
         </is>
       </c>
       <c r="B12" s="1">
-        <v>0.01233468965295748</v>
+        <v>0.01233469544468946</v>
       </c>
       <c r="C12" s="1">
-        <v>-0.0005256138244837949</v>
+        <v>-0.0005256081063282902</v>
       </c>
       <c r="D12" s="1">
-        <v>-0.004492393640905257</v>
+        <v>-0.004492441286073956</v>
       </c>
       <c r="E12" s="1">
-        <v>-8.425019875235584e-05</v>
+        <v>-8.423854350469995e-05</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -343,16 +343,16 @@
         </is>
       </c>
       <c r="B13" s="1">
-        <v>0.05137456621462233</v>
+        <v>0.05137458600928735</v>
       </c>
       <c r="C13" s="1">
-        <v>0.04387198186096963</v>
+        <v>0.04387200151438098</v>
       </c>
       <c r="D13" s="1">
-        <v>0.03904012127597367</v>
+        <v>0.03904014599696359</v>
       </c>
       <c r="E13" s="1">
-        <v>0.04441026285102501</v>
+        <v>0.04441028192319374</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -435,7 +435,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>56de3d51b4dc72f084a6addd878ba3850e32b193e20f126ef5cd6dd87c63f387</t>
+          <t>7c7299eed217b476d99cea0832704aa3fb69424e125486a2b6a652f532cac4c2</t>
         </is>
       </c>
     </row>

--- a/public/data/systems/pds/public_recent_12m_returns.xlsx
+++ b/public/data/systems/pds/public_recent_12m_returns.xlsx
@@ -79,16 +79,16 @@
         </is>
       </c>
       <c r="B2" s="1">
-        <v>-0.008810634271467555</v>
+        <v>-0.008810620202306163</v>
       </c>
       <c r="C2" s="1">
-        <v>-0.004965617259163002</v>
+        <v>-0.004965603135424046</v>
       </c>
       <c r="D2" s="1">
         <v>-0.0007589648480446076</v>
       </c>
       <c r="E2" s="1">
-        <v>-0.005403626916273052</v>
+        <v>-0.005403611163649624</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -103,16 +103,16 @@
         </is>
       </c>
       <c r="B3" s="1">
-        <v>0.02712990078219013</v>
+        <v>0.02712988111382475</v>
       </c>
       <c r="C3" s="1">
-        <v>0.04959274966310478</v>
+        <v>0.04959272956460081</v>
       </c>
       <c r="D3" s="1">
         <v>0.09694349643809308</v>
       </c>
       <c r="E3" s="1">
-        <v>0.0443725448674035</v>
+        <v>0.04437252262037705</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -127,16 +127,16 @@
         </is>
       </c>
       <c r="B4" s="1">
-        <v>-0.053625835409014</v>
+        <v>-0.05362582398650484</v>
       </c>
       <c r="C4" s="1">
-        <v>-0.04612361616690996</v>
+        <v>-0.04612360465385057</v>
       </c>
       <c r="D4" s="1">
-        <v>-0.07173190909030314</v>
+        <v>-0.07173190922506778</v>
       </c>
       <c r="E4" s="1">
-        <v>-0.04327051850581842</v>
+        <v>-0.04327050568815693</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -151,16 +151,16 @@
         </is>
       </c>
       <c r="B5" s="1">
-        <v>-0.00464628923241972</v>
+        <v>-0.004646299633217499</v>
       </c>
       <c r="C5" s="1">
-        <v>-0.02181115992490623</v>
+        <v>-0.02181117014634304</v>
       </c>
       <c r="D5" s="1">
-        <v>-0.03191396317529782</v>
+        <v>-0.03191396420405801</v>
       </c>
       <c r="E5" s="1">
-        <v>-0.02069780180194225</v>
+        <v>-0.02069781309280083</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -175,16 +175,16 @@
         </is>
       </c>
       <c r="B6" s="1">
-        <v>0.07262418701623563</v>
+        <v>0.07262418132367321</v>
       </c>
       <c r="C6" s="1">
-        <v>0.06520333136475442</v>
+        <v>0.06520332571157539</v>
       </c>
       <c r="D6" s="1">
-        <v>0.08241344964800246</v>
+        <v>0.0824134747624814</v>
       </c>
       <c r="E6" s="1">
-        <v>0.06328154323856028</v>
+        <v>0.06328153413094495</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -199,16 +199,16 @@
         </is>
       </c>
       <c r="B7" s="1">
-        <v>0.07408960113147267</v>
+        <v>0.07408958516926711</v>
       </c>
       <c r="C7" s="1">
-        <v>0.08482850228807903</v>
+        <v>0.08482848616628202</v>
       </c>
       <c r="D7" s="1">
-        <v>0.1379985646197579</v>
+        <v>0.1379985381350652</v>
       </c>
       <c r="E7" s="1">
-        <v>0.07894707003310963</v>
+        <v>0.07894705493280196</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -223,16 +223,16 @@
         </is>
       </c>
       <c r="B8" s="1">
-        <v>-0.05020755350718997</v>
+        <v>-0.05020756918776681</v>
       </c>
       <c r="C8" s="1">
-        <v>-0.07289478758558698</v>
+        <v>-0.07289480289161021</v>
       </c>
       <c r="D8" s="1">
-        <v>-0.08649241764645288</v>
+        <v>-0.08649241770493232</v>
       </c>
       <c r="E8" s="1">
-        <v>-0.07137570832534368</v>
+        <v>-0.07137572529412206</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -247,16 +247,16 @@
         </is>
       </c>
       <c r="B9" s="1">
-        <v>0.05830126368003485</v>
+        <v>0.05830125752277238</v>
       </c>
       <c r="C9" s="1">
-        <v>0.05724479666358784</v>
+        <v>0.05724479051247133</v>
       </c>
       <c r="D9" s="1">
-        <v>0.02882606636797824</v>
+        <v>0.02882606743427774</v>
       </c>
       <c r="E9" s="1">
-        <v>0.06040571936923755</v>
+        <v>0.06040571232294401</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -271,16 +271,16 @@
         </is>
       </c>
       <c r="B10" s="1">
-        <v>0.07233918564662289</v>
+        <v>0.0723392046296123</v>
       </c>
       <c r="C10" s="1">
-        <v>0.07604029163638781</v>
+        <v>0.07604031068489636</v>
       </c>
       <c r="D10" s="1">
-        <v>0.06981909459080771</v>
+        <v>0.06981909421788535</v>
       </c>
       <c r="E10" s="1">
-        <v>0.07672063070510426</v>
+        <v>0.07672065191288113</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -295,16 +295,16 @@
         </is>
       </c>
       <c r="B11" s="1">
-        <v>0.01089762242039161</v>
+        <v>0.0108976242411436</v>
       </c>
       <c r="C11" s="1">
-        <v>0.01931123399091494</v>
+        <v>0.01931123582682037</v>
       </c>
       <c r="D11" s="1">
-        <v>0.02426739656437671</v>
+        <v>0.02426739663995003</v>
       </c>
       <c r="E11" s="1">
-        <v>0.01875739785041231</v>
+        <v>0.0187573998553372</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -319,16 +319,16 @@
         </is>
       </c>
       <c r="B12" s="1">
-        <v>0.01233469544468946</v>
+        <v>0.0123346868588794</v>
       </c>
       <c r="C12" s="1">
-        <v>-0.0005256081063282902</v>
+        <v>-0.0005256165830677118</v>
       </c>
       <c r="D12" s="1">
-        <v>-0.004492441286073956</v>
+        <v>-0.004492425961924673</v>
       </c>
       <c r="E12" s="1">
-        <v>-8.423854350469995e-05</v>
+        <v>-8.42496721946695e-05</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -343,16 +343,16 @@
         </is>
       </c>
       <c r="B13" s="1">
-        <v>0.05137458600928735</v>
+        <v>0.05137459561278623</v>
       </c>
       <c r="C13" s="1">
-        <v>0.04387200151438098</v>
+        <v>0.04387201104934935</v>
       </c>
       <c r="D13" s="1">
-        <v>0.03904014599696359</v>
+        <v>0.03904014688346491</v>
       </c>
       <c r="E13" s="1">
-        <v>0.04441028192319374</v>
+        <v>0.04441029250154105</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -435,7 +435,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7c7299eed217b476d99cea0832704aa3fb69424e125486a2b6a652f532cac4c2</t>
+          <t>1db84780c3e7bdde99e91a4cc9945e53030dfa90adc2922aceb64f3893e8bda6</t>
         </is>
       </c>
     </row>
